--- a/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>KNTK</t>
   </si>
@@ -656,238 +656,250 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>348900</v>
+      </c>
+      <c r="E8" s="3">
         <v>330300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>296200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>281000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>295500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>325200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>335600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>257200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>56300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>34500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>35600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>35300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>40200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>73000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>148300</v>
+      </c>
+      <c r="E9" s="3">
         <v>153400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>114400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>121300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>124400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>151100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>158600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>124400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>20600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>19100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>18900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>40200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>200600</v>
+      </c>
+      <c r="E10" s="3">
         <v>176900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>181800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>159700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>171100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>174100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>177000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>132800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>35700</v>
-      </c>
-      <c r="L10" s="3">
-        <v>24900</v>
       </c>
       <c r="M10" s="3">
         <v>24900</v>
       </c>
       <c r="N10" s="3">
+        <v>24900</v>
+      </c>
+      <c r="O10" s="3">
         <v>24700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>16200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>21300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>32800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -906,8 +918,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -956,8 +969,11 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1006,13 +1022,16 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1900</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1027,69 +1046,72 @@
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>22900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>160400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1600</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>72700</v>
+      </c>
+      <c r="E15" s="3">
         <v>69900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>69500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>68900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>67700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>65000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>66600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>61000</v>
-      </c>
-      <c r="K15" s="3">
-        <v>4100</v>
       </c>
       <c r="L15" s="3">
         <v>4100</v>
       </c>
       <c r="M15" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="N15" s="3">
         <v>4000</v>
@@ -1101,13 +1123,16 @@
         <v>4000</v>
       </c>
       <c r="Q15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="R15" s="3">
         <v>8000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1123,108 +1148,115 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>294600</v>
+      </c>
+      <c r="E17" s="3">
         <v>291900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>258800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>253800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>250500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>279400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>317800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>233700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>192400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>20000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>22000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>21100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>23000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>21200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>42500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E18" s="3">
         <v>38400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>37500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>27200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>45000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>45800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>17800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>23500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-136100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>19000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>30500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1243,235 +1275,248 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>53500</v>
+      </c>
+      <c r="E20" s="3">
         <v>51000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>50700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>46800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>60500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>45500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>139200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>25300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>92000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>37800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>62800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>12100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>48800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>12600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-39900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-44500</v>
       </c>
     </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>180500</v>
+      </c>
+      <c r="E21" s="3">
         <v>159400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>157600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>142900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>173200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>156300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>223500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>109900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-40000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>56400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>80500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>29100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>65000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>35600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-1500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-21900</v>
       </c>
     </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>75400</v>
+      </c>
+      <c r="E22" s="3">
         <v>45000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>16100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>69300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>56700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>40500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>25300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>26800</v>
-      </c>
-      <c r="K22" s="3">
-        <v>2700</v>
       </c>
       <c r="L22" s="3">
         <v>2700</v>
       </c>
       <c r="M22" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="N22" s="3">
         <v>2600</v>
       </c>
       <c r="O22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="P22" s="3">
         <v>1200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>32400</v>
+      </c>
+      <c r="E23" s="3">
         <v>44400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>72000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>48800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>50800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>131600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>22100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-46800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>49700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>73800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>22500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>59800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>31200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-10000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-234900</v>
+      </c>
+      <c r="E24" s="3">
         <v>1300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300</v>
-      </c>
-      <c r="F24" s="3">
-        <v>400</v>
       </c>
       <c r="G24" s="3">
         <v>400</v>
       </c>
       <c r="H24" s="3">
+        <v>400</v>
+      </c>
+      <c r="I24" s="3">
         <v>1400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -1488,13 +1533,16 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="R24" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1543,108 +1591,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>267400</v>
+      </c>
+      <c r="E26" s="3">
         <v>43100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>71700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>48500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>49400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>131400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>21400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-46800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>49700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>73800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>22500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>59800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>31200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-25400</v>
       </c>
     </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E27" s="3">
         <v>11200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>20600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-2700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>43700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>8900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1693,8 +1750,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1743,8 +1803,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1793,8 +1856,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1843,108 +1909,117 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-53500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-51000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-50700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-46800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-60500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-45500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-139200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-25300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-92000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-37800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-62800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-12100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-48800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>39900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E33" s="3">
         <v>11200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>20600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-2700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>43700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>8900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1993,113 +2068,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E35" s="3">
         <v>11200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>20600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-2700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>43700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>8900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2118,8 +2202,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2138,58 +2223,62 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E41" s="3">
         <v>100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>132000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>109000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>75100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>51300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2238,334 +2327,355 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>215700</v>
+      </c>
+      <c r="E43" s="3">
         <v>230600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>181500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>199000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>204000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>269600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>296200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>262600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>25800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>12000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>13700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E44" s="3">
         <v>9100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>7300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>13100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>13000</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E45" s="3">
         <v>48700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>56800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>41000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>26600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>24300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>27200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>29200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5900</v>
-      </c>
-      <c r="L45" s="3">
-        <v>6000</v>
       </c>
       <c r="M45" s="3">
         <v>6000</v>
       </c>
       <c r="N45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="O45" s="3">
         <v>7800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>257300</v>
+      </c>
+      <c r="E46" s="3">
         <v>288500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>247800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>246200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>241900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>318800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>341800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>309500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>166600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>130300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>98200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>76200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>42800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>20400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>20900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>37500</v>
       </c>
     </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2541200</v>
+      </c>
+      <c r="E47" s="3">
         <v>2521700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2490100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2413000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2381300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2372600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2342300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2361300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1364800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1537900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1554400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1566700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1555200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1524400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1408500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1336800</v>
       </c>
     </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2780800</v>
+      </c>
+      <c r="E48" s="3">
         <v>2768500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2750500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2698300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2563800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2563300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2534100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2535100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>187000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>189400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>190800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>193400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>195800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>205300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>207300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>596700</v>
+      </c>
+      <c r="E49" s="3">
         <v>625900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>655000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>681600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>700500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>726900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>751800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>776900</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>8</v>
@@ -2579,8 +2689,8 @@
       <c r="O49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P49" s="3">
-        <v>0</v>
+      <c r="P49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q49" s="3">
         <v>0</v>
@@ -2588,8 +2698,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2638,8 +2751,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2688,58 +2804,64 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>320900</v>
+      </c>
+      <c r="E52" s="3">
         <v>81500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>83500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>85600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>32300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>26400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>6200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2788,58 +2910,64 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6496900</v>
+      </c>
+      <c r="E54" s="3">
         <v>6286000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6226900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6124700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5919700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6007200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5996300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6013700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1724700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1865900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1853700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1842600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1799600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1756400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1642200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1588500</v>
       </c>
     </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2858,8 +2986,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2878,34 +3007,35 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E57" s="3">
         <v>17600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>10900</v>
       </c>
       <c r="J57" s="3">
         <v>10900</v>
       </c>
       <c r="K57" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -2917,19 +3047,22 @@
         <v>0</v>
       </c>
       <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
         <v>18800</v>
       </c>
-      <c r="P57" s="3" t="s">
+      <c r="Q57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>200</v>
       </c>
-      <c r="R57" s="3" t="s">
+      <c r="S57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2942,8 +3075,8 @@
       <c r="F58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
+      <c r="G58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -2952,10 +3085,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>54300</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>8</v>
@@ -2966,8 +3099,8 @@
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -2978,134 +3111,143 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>216100</v>
+      </c>
+      <c r="E59" s="3">
         <v>233500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>163100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>230000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>209900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>268700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>295100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>323400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>27200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>27500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>25100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>11200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>250100</v>
+      </c>
+      <c r="E60" s="3">
         <v>251100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>199400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>248300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>227800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>284700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>306000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>388600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>27200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>25100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>21900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>30000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>16500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>12100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3562800</v>
+      </c>
+      <c r="E61" s="3">
         <v>3607000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3625800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3511600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3368500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3447500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2971300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2894000</v>
-      </c>
-      <c r="K61" s="3">
-        <v>657000</v>
       </c>
       <c r="L61" s="3">
         <v>657000</v>
@@ -3117,69 +3259,75 @@
         <v>657000</v>
       </c>
       <c r="O61" s="3">
+        <v>657000</v>
+      </c>
+      <c r="P61" s="3">
         <v>624000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>580000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>493000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>468000</v>
       </c>
     </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E62" s="3">
         <v>57500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>64900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>90000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>50700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>47700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>85800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>222700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>135300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>193700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>197500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>227500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>208600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>247800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>243500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>232300</v>
       </c>
     </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3228,8 +3376,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3278,8 +3429,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3328,58 +3482,64 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7027700</v>
+      </c>
+      <c r="E66" s="3">
         <v>7124000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7132700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6760900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6759500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6841700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7177700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7151500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2301900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2350100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2359900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2173600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2046100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1683600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1571900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1518000</v>
       </c>
     </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3398,8 +3558,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3448,8 +3609,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3498,8 +3662,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3548,8 +3715,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3598,58 +3768,64 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-723500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-929800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-902400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-863500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-958600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-941700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1181300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1137900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-577300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-484100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-506200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-369300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-391000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-400400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-402700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-402500</v>
       </c>
     </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3698,8 +3874,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3748,8 +3927,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3798,58 +3980,64 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-530800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-838000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-905800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-636200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-839800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-834600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1181300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1137900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-577200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-484100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-506200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-331000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-246500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>72800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>70300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3898,113 +4086,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E81" s="3">
         <v>11200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>20600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-2700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>43700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>8900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4023,40 +4220,41 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>72700</v>
+      </c>
+      <c r="E83" s="3">
         <v>69900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>69500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>68900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>67700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>65000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>66600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>61000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4100</v>
       </c>
       <c r="L83" s="3">
         <v>4100</v>
       </c>
       <c r="M83" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="N83" s="3">
         <v>4000</v>
@@ -4068,13 +4266,16 @@
         <v>4000</v>
       </c>
       <c r="Q83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="R83" s="3">
         <v>8000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4123,8 +4324,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4173,8 +4377,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4223,8 +4430,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4273,8 +4483,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4323,58 +4536,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>178900</v>
+      </c>
+      <c r="E89" s="3">
         <v>174500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>111500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>119600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>159800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>184300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>170500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>98400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>51300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>57300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>57800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>43300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>26800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>50700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>86800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4393,58 +4612,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-68700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-86800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-105500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-68600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-47800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-93900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-47200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-32800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-26500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4493,8 +4716,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4543,58 +4769,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-103700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-134700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-201400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-246500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-69700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-147400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-49700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>7600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>12500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-37100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-126000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-175300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-97600</v>
       </c>
     </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4613,8 +4845,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4628,19 +4861,19 @@
         <v>-200</v>
       </c>
       <c r="G96" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H96" s="3">
         <v>-300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-400</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
       <c r="K96" s="3">
-        <v>-5600</v>
+        <v>0</v>
       </c>
       <c r="L96" s="3">
         <v>-5600</v>
@@ -4652,7 +4885,7 @@
         <v>-5600</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>-5600</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -4663,8 +4896,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4713,8 +4949,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4763,8 +5002,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4813,34 +5055,37 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-70700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-42000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>90200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>122500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-95400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-30600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-133200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-80100</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-35900</v>
       </c>
       <c r="L100" s="3">
         <v>-35900</v>
@@ -4849,22 +5094,25 @@
         <v>-35900</v>
       </c>
       <c r="N100" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="O100" s="3">
         <v>-2900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>32400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>75400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>84400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4913,54 +5161,60 @@
       <c r="R101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-12300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>23000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>33900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>23800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>27100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>22200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
   <si>
     <t>KNTK</t>
   </si>
@@ -656,250 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>341400</v>
+      </c>
+      <c r="E8" s="3">
         <v>348900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>330300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>296200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>281000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>295500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>325200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>335600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>257200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>56300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>34500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>35600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>35300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>40200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>73000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E9" s="3">
         <v>148300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>153400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>114400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>121300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>124400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>151100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>158600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>124400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>20600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>10700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>19100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>18900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>40200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>181400</v>
+      </c>
+      <c r="E10" s="3">
         <v>200600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>176900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>181800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>159700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>171100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>174100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>177000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>132800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>35700</v>
-      </c>
-      <c r="M10" s="3">
-        <v>24900</v>
       </c>
       <c r="N10" s="3">
         <v>24900</v>
       </c>
       <c r="O10" s="3">
+        <v>24900</v>
+      </c>
+      <c r="P10" s="3">
         <v>24700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>16200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>21300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>32800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -919,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,17 +1042,20 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>1900</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
@@ -1049,72 +1069,75 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>22900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-4500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>160400</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1600</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E15" s="3">
         <v>72700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>69900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>69500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>68900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>67700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>65000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>66600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>61000</v>
-      </c>
-      <c r="L15" s="3">
-        <v>4100</v>
       </c>
       <c r="M15" s="3">
         <v>4100</v>
       </c>
       <c r="N15" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="O15" s="3">
         <v>4000</v>
@@ -1126,13 +1149,16 @@
         <v>4000</v>
       </c>
       <c r="R15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="S15" s="3">
         <v>8000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>315300</v>
+      </c>
+      <c r="E17" s="3">
         <v>294600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>291900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>258800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>253800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>250500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>279400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>317800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>233700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>192400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>20000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>22000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>23000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>42500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E18" s="3">
         <v>54300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>38400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>37500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>27200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>45000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>45800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>23500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-136100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>19000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>30500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,250 +1309,263 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>60600</v>
+      </c>
+      <c r="E20" s="3">
         <v>53500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>51000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>50700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>46800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>60500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>45500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>139200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>25300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>92000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>37800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>62800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>12100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>48800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>12600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-39900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-44500</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>160300</v>
+      </c>
+      <c r="E21" s="3">
         <v>180500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>159400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>157600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>142900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>173200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>156300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>223500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>109900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-40000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>56400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>80500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>29100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>65000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>35600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-1500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-21900</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E22" s="3">
         <v>75400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>45000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>16100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>69300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>56700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>40500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>25300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>26800</v>
-      </c>
-      <c r="L22" s="3">
-        <v>2700</v>
       </c>
       <c r="M22" s="3">
         <v>2700</v>
       </c>
       <c r="N22" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="O22" s="3">
         <v>2600</v>
       </c>
       <c r="P22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Q22" s="3">
         <v>1200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E23" s="3">
         <v>32400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>44400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>72000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>48800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>50800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>131600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>22100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-46800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>49700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>73800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>22500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>59800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>31200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-10000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-234900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>400</v>
       </c>
       <c r="H24" s="3">
         <v>400</v>
       </c>
       <c r="I24" s="3">
+        <v>400</v>
+      </c>
+      <c r="J24" s="3">
         <v>1400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1536,13 +1582,16 @@
         <v>0</v>
       </c>
       <c r="R24" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="S24" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E26" s="3">
         <v>267400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>43100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>71700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>48500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>49400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>131400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>21400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-46800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>49700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>73800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>22500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>59800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>31200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-9300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-25400</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E27" s="3">
         <v>243000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>11200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>20600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-2700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>43700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-9000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1806,8 +1867,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,114 +1979,123 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-60600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-53500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-51000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-50700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-46800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-60500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-45500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-139200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-25300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-92000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-37800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-62800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-12100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-48800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-12600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>39900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E33" s="3">
         <v>243000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>11200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>20600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-2700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>43700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>8900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-9000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E35" s="3">
         <v>243000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>11200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>20600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-2700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>43700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>8900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-9000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,61 +2310,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E41" s="3">
         <v>4500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>132000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>109000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>75100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>51300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2330,167 +2420,179 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>209900</v>
+      </c>
+      <c r="E43" s="3">
         <v>215700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>230600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>181500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>199000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>204000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>269600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>296200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>262600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>25800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>12000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>13700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>3100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>7300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>13100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>13000</v>
       </c>
-      <c r="K44" s="3" t="s">
+      <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E45" s="3">
         <v>34000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>48700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>56800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>41000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>26600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>24300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>27200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5900</v>
-      </c>
-      <c r="M45" s="3">
-        <v>6000</v>
       </c>
       <c r="N45" s="3">
         <v>6000</v>
       </c>
       <c r="O45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="P45" s="3">
         <v>7800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2498,187 +2600,196 @@
         <v>257300</v>
       </c>
       <c r="E46" s="3">
+        <v>257300</v>
+      </c>
+      <c r="F46" s="3">
         <v>288500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>247800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>246200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>241900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>318800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>341800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>309500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>166600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>130300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>98200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>76200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>42800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>20400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>20900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>37500</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2526300</v>
+      </c>
+      <c r="E47" s="3">
         <v>2541200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2521700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2490100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2413000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2381300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2372600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2342300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2361300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1364800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1537900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1554400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1566700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1555200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1524400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1408500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1336800</v>
       </c>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2774500</v>
+      </c>
+      <c r="E48" s="3">
         <v>2780800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2768500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2750500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2698300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2563800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2563300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2534100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2535100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>187000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>189400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>190800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>193400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>195800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>205300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>207300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>567900</v>
+      </c>
+      <c r="E49" s="3">
         <v>596700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>625900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>655000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>681600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>700500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>726900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>751800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>776900</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>8</v>
@@ -2692,8 +2803,8 @@
       <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
+      <c r="Q49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R49" s="3">
         <v>0</v>
@@ -2701,8 +2812,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,61 +2924,67 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>321600</v>
+      </c>
+      <c r="E52" s="3">
         <v>320900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>81500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>83500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>85600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>32300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>25500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>26400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6447600</v>
+      </c>
+      <c r="E54" s="3">
         <v>6496900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6286000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6226900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6124700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5919700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6007200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5996300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6013700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1724700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1865900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1853700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1842600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1799600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1756400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1642200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1588500</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,37 +3138,38 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E57" s="3">
         <v>34000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>36200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>10900</v>
       </c>
       <c r="K57" s="3">
         <v>10900</v>
       </c>
       <c r="L57" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -3050,33 +3181,36 @@
         <v>0</v>
       </c>
       <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
         <v>18800</v>
       </c>
-      <c r="Q57" s="3" t="s">
+      <c r="R57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>200</v>
       </c>
-      <c r="S57" s="3" t="s">
+      <c r="T57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -3088,10 +3222,10 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>54300</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
@@ -3102,8 +3236,8 @@
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -3114,143 +3248,152 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>217500</v>
+      </c>
+      <c r="E59" s="3">
         <v>216100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>233500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>163100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>230000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>209900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>268700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>295100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>323400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>27200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>25100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>11200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>234000</v>
+      </c>
+      <c r="E60" s="3">
         <v>250100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>251100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>199400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>248300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>227800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>284700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>306000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>388600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>27200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>25100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>21900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>30000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>16500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>12100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3517100</v>
+      </c>
+      <c r="E61" s="3">
         <v>3562800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3607000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3625800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3511600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3368500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3447500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2971300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2894000</v>
-      </c>
-      <c r="L61" s="3">
-        <v>657000</v>
       </c>
       <c r="M61" s="3">
         <v>657000</v>
@@ -3262,72 +3405,78 @@
         <v>657000</v>
       </c>
       <c r="P61" s="3">
+        <v>657000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>624000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>580000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>493000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>468000</v>
       </c>
     </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E62" s="3">
         <v>56900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>57500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>64900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>90000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>50700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>47700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>85800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>222700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>135300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>193700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>197500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>227500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>208600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>247800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>243500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>232300</v>
       </c>
     </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7421000</v>
+      </c>
+      <c r="E66" s="3">
         <v>7027700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7124000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7132700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6760900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6759500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6841700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7177700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7151500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2301900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2350100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2359900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2173600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2046100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1683600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1571900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1518000</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-973500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-723500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-929800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-902400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-863500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-958600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-941700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1181300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1137900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-577300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-484100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-506200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-369300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-391000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-400400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-402700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-402500</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-973400</v>
+      </c>
+      <c r="E76" s="3">
         <v>-530800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-838000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-905800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-636200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-839800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-834600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1181300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1137900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-577200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-484100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-506200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-331000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-246500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>72800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>70300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E81" s="3">
         <v>243000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>11200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>20600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-2700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>43700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>8900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-9000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,43 +4419,44 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E83" s="3">
         <v>72700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>69900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>69500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>68900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>67700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>65000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>66600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>61000</v>
-      </c>
-      <c r="L83" s="3">
-        <v>4100</v>
       </c>
       <c r="M83" s="3">
         <v>4100</v>
       </c>
       <c r="N83" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="O83" s="3">
         <v>4000</v>
@@ -4269,13 +4468,16 @@
         <v>4000</v>
       </c>
       <c r="R83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="S83" s="3">
         <v>8000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>153700</v>
+      </c>
+      <c r="E89" s="3">
         <v>178900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>174500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>111500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>119600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>159800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>184300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>170500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>98400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>51300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>57300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>57800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>43300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>26800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>50700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>86800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,61 +4833,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-60200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-68700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-86800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-105500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-68600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-47800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-93900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-47200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-32800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-26500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-62000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-103700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-134700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-201400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-246500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-69700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-147400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-49700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-19400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>7600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>12500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>1900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-37100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-126000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-175300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-97600</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,13 +5079,14 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-200</v>
+        <v>-700</v>
       </c>
       <c r="E96" s="3">
         <v>-200</v>
@@ -4864,19 +5098,19 @@
         <v>-200</v>
       </c>
       <c r="H96" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I96" s="3">
         <v>-300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-400</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
       <c r="L96" s="3">
-        <v>-5600</v>
+        <v>0</v>
       </c>
       <c r="M96" s="3">
         <v>-5600</v>
@@ -4888,7 +5122,7 @@
         <v>-5600</v>
       </c>
       <c r="P96" s="3">
-        <v>0</v>
+        <v>-5600</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -4899,8 +5133,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,37 +5301,40 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-86500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-70700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-42000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>90200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>122500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-95400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-30600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-133200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-80100</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-35900</v>
       </c>
       <c r="M100" s="3">
         <v>-35900</v>
@@ -5097,22 +5343,25 @@
         <v>-35900</v>
       </c>
       <c r="O100" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="P100" s="3">
         <v>-2900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>32400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>75400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>84400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5164,57 +5413,63 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E102" s="3">
         <v>4400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>23000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>33900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>23800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>27100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>22200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>KNTK</t>
   </si>
@@ -656,263 +656,276 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>359500</v>
+      </c>
+      <c r="E8" s="3">
         <v>341400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>348900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>330300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>296200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>281000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>295500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>325200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>335600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>257200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>56300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>34500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>35600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>35300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>40200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>73000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>152700</v>
+      </c>
+      <c r="E9" s="3">
         <v>160000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>148300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>153400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>114400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>121300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>124400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>151100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>158600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>124400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>20600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>9600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>10700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>19100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>18900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>40200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>206800</v>
+      </c>
+      <c r="E10" s="3">
         <v>181400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>200600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>176900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>181800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>159700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>171100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>174100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>177000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>132800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>35700</v>
-      </c>
-      <c r="N10" s="3">
-        <v>24900</v>
       </c>
       <c r="O10" s="3">
         <v>24900</v>
       </c>
       <c r="P10" s="3">
+        <v>24900</v>
+      </c>
+      <c r="Q10" s="3">
         <v>24700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>16200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>21300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>32800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -933,8 +946,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -989,8 +1003,11 @@
       <c r="T12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1045,20 +1062,23 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>500</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1900</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
@@ -1072,75 +1092,78 @@
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>22900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-4500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>160400</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1600</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>75100</v>
+      </c>
+      <c r="E15" s="3">
         <v>73600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>72700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>69900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>69500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>68900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>67700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>65000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>66600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>61000</v>
-      </c>
-      <c r="M15" s="3">
-        <v>4100</v>
       </c>
       <c r="N15" s="3">
         <v>4100</v>
       </c>
       <c r="O15" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="P15" s="3">
         <v>4000</v>
@@ -1152,13 +1175,16 @@
         <v>4000</v>
       </c>
       <c r="S15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T15" s="3">
         <v>8000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1176,120 +1202,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>303400</v>
+      </c>
+      <c r="E17" s="3">
         <v>315300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>294600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>291900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>258800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>253800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>250500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>279400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>317800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>233700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>192400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>20000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>22000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>21100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>23000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>42500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E18" s="3">
         <v>26100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>54300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>38400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>37500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>27200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>45000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>45800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>23500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-136100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>19000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>30500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1310,265 +1343,278 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>116100</v>
+      </c>
+      <c r="E20" s="3">
         <v>60600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>53500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>51000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>50700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>46800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>60500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>45500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>139200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>25300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>92000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>37800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>62800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>12100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>48800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>12600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-39900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-44500</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>247300</v>
+      </c>
+      <c r="E21" s="3">
         <v>160300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>180500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>159400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>157600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>142900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>173200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>156300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>223500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>109900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-40000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>56400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>80500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>29100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>65000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>35600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-1500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-21900</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E22" s="3">
         <v>47500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>75400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>45000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>16100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>69300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>56700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>40500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>25300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>26800</v>
-      </c>
-      <c r="M22" s="3">
-        <v>2700</v>
       </c>
       <c r="N22" s="3">
         <v>2700</v>
       </c>
       <c r="O22" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="P22" s="3">
         <v>2600</v>
       </c>
       <c r="Q22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="R22" s="3">
         <v>1200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>118200</v>
+      </c>
+      <c r="E23" s="3">
         <v>39200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>32400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>44400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>72000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>48800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>50800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>131600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>22100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-46800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>49700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>73800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>22500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>59800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>31200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-10000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E24" s="3">
         <v>3800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-234900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>400</v>
       </c>
       <c r="I24" s="3">
         <v>400</v>
       </c>
       <c r="J24" s="3">
+        <v>400</v>
+      </c>
+      <c r="K24" s="3">
         <v>1400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1585,13 +1631,16 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="T24" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1646,120 +1695,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>108900</v>
+      </c>
+      <c r="E26" s="3">
         <v>35400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>267400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>43100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>71700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>48500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>49400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>131400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>21400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-46800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>49700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>73800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>22500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>59800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>31200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-9300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-25400</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7200</v>
+        <v>32600</v>
       </c>
       <c r="E27" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F27" s="3">
         <v>243000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>11200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>20600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-2700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>43700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>8900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-9000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1814,8 +1872,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1870,8 +1931,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1926,8 +1990,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1982,120 +2049,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-116100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-60600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-53500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-51000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-50700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-46800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-60500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-45500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-139200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-25300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-92000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-37800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-62800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-48800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-12600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>39900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>7200</v>
+        <v>32600</v>
       </c>
       <c r="E33" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F33" s="3">
         <v>243000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>11200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>20600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-2700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>43700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>8900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-9000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2150,125 +2226,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>7200</v>
+        <v>32600</v>
       </c>
       <c r="E35" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F35" s="3">
         <v>243000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>11200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>20600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-2700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>43700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>8900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-9000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2289,8 +2374,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2311,64 +2397,68 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E41" s="3">
         <v>9800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>132000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>109000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>75100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>51300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2423,376 +2513,397 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>243200</v>
+      </c>
+      <c r="E43" s="3">
         <v>209900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>215700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>230600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>181500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>199000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>204000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>269600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>296200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>262600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>25800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>12000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>13700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3">
         <v>3100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>7300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>4200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>4800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>13100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13000</v>
       </c>
-      <c r="L44" s="3" t="s">
+      <c r="M44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E45" s="3">
         <v>37700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>34000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>48700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>56800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>41000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>26600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>24300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>29200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5900</v>
-      </c>
-      <c r="N45" s="3">
-        <v>6000</v>
       </c>
       <c r="O45" s="3">
         <v>6000</v>
       </c>
       <c r="P45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="Q45" s="3">
         <v>7800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>257300</v>
+        <v>299300</v>
       </c>
       <c r="E46" s="3">
         <v>257300</v>
       </c>
       <c r="F46" s="3">
+        <v>257300</v>
+      </c>
+      <c r="G46" s="3">
         <v>288500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>247800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>246200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>241900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>318800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>341800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>309500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>166600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>130300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>98200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>76200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>42800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>20400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>20900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>37500</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2075900</v>
+      </c>
+      <c r="E47" s="3">
         <v>2526300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2541200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2521700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2490100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2413000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2381300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2372600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2342300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2361300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1364800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1537900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1554400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1566700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1555200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1524400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1408500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1336800</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3240200</v>
+      </c>
+      <c r="E48" s="3">
         <v>2774500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2780800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2768500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2750500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2698300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2563800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2563300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2534100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2535100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>187000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>189400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>190800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>193400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>195800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>205300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>207300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>951700</v>
+      </c>
+      <c r="E49" s="3">
         <v>567900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>596700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>625900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>655000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>681600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>700500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>726900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>751800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>776900</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>8</v>
@@ -2806,8 +2917,8 @@
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R49" s="3">
-        <v>0</v>
+      <c r="R49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S49" s="3">
         <v>0</v>
@@ -2815,8 +2926,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2871,8 +2985,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2927,64 +3044,70 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>293100</v>
+      </c>
+      <c r="E52" s="3">
         <v>321600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>320900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>81500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>83500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>85600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>32300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>26400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>30900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3039,64 +3162,70 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6860300</v>
+      </c>
+      <c r="E54" s="3">
         <v>6447600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6496900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6286000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6226900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6124700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5919700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6007200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5996300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6013700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1724700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1865900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1853700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1842600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1799600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1756400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1642200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1588500</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3117,8 +3246,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3139,40 +3269,41 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>44500</v>
+      </c>
+      <c r="E57" s="3">
         <v>16500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>34000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>36200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>18300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>10900</v>
       </c>
       <c r="L57" s="3">
         <v>10900</v>
       </c>
       <c r="M57" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="N57" s="3">
         <v>0</v>
@@ -3184,39 +3315,42 @@
         <v>0</v>
       </c>
       <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3">
         <v>18800</v>
       </c>
-      <c r="R57" s="3" t="s">
+      <c r="S57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>200</v>
       </c>
-      <c r="T57" s="3" t="s">
+      <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
+        <v>148800</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -3225,10 +3359,10 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>54300</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
@@ -3239,8 +3373,8 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3251,152 +3385,161 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>205600</v>
+      </c>
+      <c r="E59" s="3">
         <v>217500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>216100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>233500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>163100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>230000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>209900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>268700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>295100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>323400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>25100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>11200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>398900</v>
+      </c>
+      <c r="E60" s="3">
         <v>234000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>250100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>251100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>199400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>248300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>227800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>284700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>306000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>388600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>27200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>25100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>21900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>30000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>16500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>12100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3258400</v>
+      </c>
+      <c r="E61" s="3">
         <v>3517100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3562800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3607000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3625800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3511600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3368500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3447500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2971300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2894000</v>
-      </c>
-      <c r="M61" s="3">
-        <v>657000</v>
       </c>
       <c r="N61" s="3">
         <v>657000</v>
@@ -3408,75 +3551,81 @@
         <v>657000</v>
       </c>
       <c r="Q61" s="3">
+        <v>657000</v>
+      </c>
+      <c r="R61" s="3">
         <v>624000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>580000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>493000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>468000</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>120300</v>
+      </c>
+      <c r="E62" s="3">
         <v>45300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>56900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>57500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>64900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>90000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>50700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>47700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>85800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>222700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>135300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>193700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>197500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>227500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>208600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>247800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>243500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>232300</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3531,8 +3680,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3587,8 +3739,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3643,64 +3798,70 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8067200</v>
+      </c>
+      <c r="E66" s="3">
         <v>7421000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7027700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7124000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7132700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6760900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6759500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6841700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7177700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7151500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2301900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2350100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2359900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2173600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2046100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1683600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1571900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1518000</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3721,8 +3882,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3777,8 +3939,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3833,8 +3998,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3889,8 +4057,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3945,64 +4116,70 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1206900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-973500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-723500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-929800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-902400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-863500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-958600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-941700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1181300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1137900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-577300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-484100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-506200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-369300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-391000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-400400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-402700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-402500</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4057,8 +4234,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4113,8 +4293,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4169,64 +4352,70 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1206900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-973400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-530800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-838000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-905800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-636200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-839800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-834600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-1181300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1137900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-577200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-484100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-506200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-331000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-246500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>72800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>70300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4281,125 +4470,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>7200</v>
+        <v>32600</v>
       </c>
       <c r="E81" s="3">
+        <v>7400</v>
+      </c>
+      <c r="F81" s="3">
         <v>243000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>11200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>20600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-2700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>43700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>8900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-9000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4420,46 +4618,47 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>75100</v>
+      </c>
+      <c r="E83" s="3">
         <v>73600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>72700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>69900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>69500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>68900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>67700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>65000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>66600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>61000</v>
-      </c>
-      <c r="M83" s="3">
-        <v>4100</v>
       </c>
       <c r="N83" s="3">
         <v>4100</v>
       </c>
       <c r="O83" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="P83" s="3">
         <v>4000</v>
@@ -4471,13 +4670,16 @@
         <v>4000</v>
       </c>
       <c r="S83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="T83" s="3">
         <v>8000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4532,8 +4734,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4588,8 +4793,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4644,8 +4852,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4700,8 +4911,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4756,64 +4970,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>125500</v>
+      </c>
+      <c r="E89" s="3">
         <v>153700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>178900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>174500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>111500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>119600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>159800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>184300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>170500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>98400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>51300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>57300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>57800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>43300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>26800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>50700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>86800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4834,64 +5054,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-39900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-60200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-68700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-86800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-105500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-68600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-47800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-93900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-47200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-32800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-26500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4946,8 +5170,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5002,64 +5229,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>105300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-62000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-103700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-134700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-201400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-246500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-69700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-147400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-49700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-19400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>7600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>12500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-37100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-126000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-175300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-97600</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5080,16 +5313,17 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-70500</v>
+      </c>
+      <c r="E96" s="3">
         <v>-700</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-200</v>
       </c>
       <c r="F96" s="3">
         <v>-200</v>
@@ -5101,19 +5335,19 @@
         <v>-200</v>
       </c>
       <c r="I96" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J96" s="3">
         <v>-300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-400</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
-        <v>-5600</v>
+        <v>0</v>
       </c>
       <c r="N96" s="3">
         <v>-5600</v>
@@ -5125,7 +5359,7 @@
         <v>-5600</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>-5600</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -5136,8 +5370,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5192,8 +5429,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5248,8 +5488,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5304,40 +5547,43 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-228000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-86500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-70700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-42000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>90200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>122500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-95400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-30600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-133200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-80100</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-35900</v>
       </c>
       <c r="N100" s="3">
         <v>-35900</v>
@@ -5346,22 +5592,25 @@
         <v>-35900</v>
       </c>
       <c r="P100" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>32400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>75400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>84400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5416,60 +5665,66 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E102" s="3">
         <v>5200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>23000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>33900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>23800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>27100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>22200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>KNTK</t>
   </si>
@@ -656,276 +656,289 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>396400</v>
+      </c>
+      <c r="E8" s="3">
         <v>359500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>341400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>348900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>330300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>296200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>281000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>295500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>325200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>335600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>257200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>56300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>34500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>35600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>34100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>35300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>40200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>73000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>152700</v>
+        <v>199000</v>
       </c>
       <c r="E9" s="3">
-        <v>160000</v>
+        <v>190600</v>
       </c>
       <c r="F9" s="3">
-        <v>148300</v>
+        <v>197100</v>
       </c>
       <c r="G9" s="3">
-        <v>153400</v>
+        <v>184300</v>
       </c>
       <c r="H9" s="3">
-        <v>114400</v>
+        <v>190700</v>
       </c>
       <c r="I9" s="3">
-        <v>121300</v>
+        <v>150400</v>
       </c>
       <c r="J9" s="3">
+        <v>151900</v>
+      </c>
+      <c r="K9" s="3">
         <v>124400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>151100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>158600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>124400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>20600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>9600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>19100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>18900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>40200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>206800</v>
+        <v>197400</v>
       </c>
       <c r="E10" s="3">
-        <v>181400</v>
+        <v>168900</v>
       </c>
       <c r="F10" s="3">
-        <v>200600</v>
+        <v>144300</v>
       </c>
       <c r="G10" s="3">
-        <v>176900</v>
+        <v>164500</v>
       </c>
       <c r="H10" s="3">
-        <v>181800</v>
+        <v>139600</v>
       </c>
       <c r="I10" s="3">
-        <v>159700</v>
+        <v>145800</v>
       </c>
       <c r="J10" s="3">
+        <v>129200</v>
+      </c>
+      <c r="K10" s="3">
         <v>171100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>174100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>177000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>132800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>35700</v>
-      </c>
-      <c r="O10" s="3">
-        <v>24900</v>
       </c>
       <c r="P10" s="3">
         <v>24900</v>
       </c>
       <c r="Q10" s="3">
+        <v>24900</v>
+      </c>
+      <c r="R10" s="3">
         <v>24700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>16200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>21300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>32800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,8 +960,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1006,8 +1020,11 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1065,108 +1082,114 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>500</v>
+        <v>-28600</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-56200</v>
       </c>
       <c r="F14" s="3">
-        <v>1900</v>
+        <v>4200</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>2900</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>12100</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>22900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-4500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>160400</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1600</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>87600</v>
+      </c>
+      <c r="E15" s="3">
         <v>75100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>73600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>72700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>69900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>69500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>68900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>67700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>65000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>66600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>61000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>4100</v>
       </c>
       <c r="O15" s="3">
         <v>4100</v>
       </c>
       <c r="P15" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="Q15" s="3">
         <v>4000</v>
@@ -1178,13 +1201,16 @@
         <v>4000</v>
       </c>
       <c r="T15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="U15" s="3">
         <v>8000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1203,126 +1229,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>303400</v>
+        <v>322100</v>
       </c>
       <c r="E17" s="3">
-        <v>315300</v>
+        <v>299700</v>
       </c>
       <c r="F17" s="3">
-        <v>294600</v>
+        <v>311100</v>
       </c>
       <c r="G17" s="3">
-        <v>291900</v>
+        <v>286900</v>
       </c>
       <c r="H17" s="3">
-        <v>258800</v>
+        <v>289000</v>
       </c>
       <c r="I17" s="3">
-        <v>253800</v>
+        <v>246600</v>
       </c>
       <c r="J17" s="3">
+        <v>253400</v>
+      </c>
+      <c r="K17" s="3">
         <v>250500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>279400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>317800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>233700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>192400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>20000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>22000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>23000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>42500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>56100</v>
+        <v>74300</v>
       </c>
       <c r="E18" s="3">
-        <v>26100</v>
+        <v>59700</v>
       </c>
       <c r="F18" s="3">
-        <v>54300</v>
+        <v>30300</v>
       </c>
       <c r="G18" s="3">
-        <v>38400</v>
+        <v>61900</v>
       </c>
       <c r="H18" s="3">
-        <v>37500</v>
+        <v>41300</v>
       </c>
       <c r="I18" s="3">
-        <v>27200</v>
+        <v>49600</v>
       </c>
       <c r="J18" s="3">
+        <v>27600</v>
+      </c>
+      <c r="K18" s="3">
         <v>45000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>45800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>23500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-136100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>19000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>30500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1344,280 +1377,293 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>116100</v>
+        <v>-54500</v>
       </c>
       <c r="E20" s="3">
-        <v>60600</v>
+        <v>-56000</v>
       </c>
       <c r="F20" s="3">
-        <v>53500</v>
+        <v>-60500</v>
       </c>
       <c r="G20" s="3">
-        <v>51000</v>
+        <v>-51900</v>
       </c>
       <c r="H20" s="3">
-        <v>50700</v>
+        <v>-50800</v>
       </c>
       <c r="I20" s="3">
-        <v>46800</v>
+        <v>-49600</v>
       </c>
       <c r="J20" s="3">
+        <v>-46500</v>
+      </c>
+      <c r="K20" s="3">
         <v>60500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>45500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>139200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>25300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>92000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>37800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>62800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>12100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>48800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>12600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-39900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-44500</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>247300</v>
+        <v>216400</v>
       </c>
       <c r="E21" s="3">
-        <v>160300</v>
+        <v>190800</v>
       </c>
       <c r="F21" s="3">
-        <v>180500</v>
+        <v>164300</v>
       </c>
       <c r="G21" s="3">
-        <v>159400</v>
+        <v>186500</v>
       </c>
       <c r="H21" s="3">
-        <v>157600</v>
+        <v>162000</v>
       </c>
       <c r="I21" s="3">
-        <v>142900</v>
+        <v>168700</v>
       </c>
       <c r="J21" s="3">
+        <v>143000</v>
+      </c>
+      <c r="K21" s="3">
         <v>173200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>156300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>223500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>109900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-40000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>56400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>80500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>29100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>65000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>35600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-1500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-21900</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E22" s="3">
         <v>54000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>47500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>75400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>45000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>16100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>69300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>56700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>40500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>25300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>26800</v>
-      </c>
-      <c r="N22" s="3">
-        <v>2700</v>
       </c>
       <c r="O22" s="3">
         <v>2700</v>
       </c>
       <c r="P22" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="Q22" s="3">
         <v>2600</v>
       </c>
       <c r="R22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="S22" s="3">
         <v>1200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>91900</v>
+      </c>
+      <c r="E23" s="3">
         <v>118200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>39200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>32400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>44400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>72000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>48800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>50800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>131600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>22100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-46800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>49700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>73800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>22500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>59800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>31200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-10000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E24" s="3">
         <v>9200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-234900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
-      </c>
-      <c r="I24" s="3">
-        <v>400</v>
       </c>
       <c r="J24" s="3">
         <v>400</v>
       </c>
       <c r="K24" s="3">
+        <v>400</v>
+      </c>
+      <c r="L24" s="3">
         <v>1400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>700</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
@@ -1634,13 +1680,16 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="U24" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1698,126 +1747,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>83700</v>
+      </c>
+      <c r="E26" s="3">
         <v>108900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>35400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>267400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>43100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>71700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>48500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>49400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>131400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>21400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-46800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>49700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>73800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>22500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>59800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>31200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-25400</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E27" s="3">
         <v>32600</v>
       </c>
-      <c r="E27" s="3">
-        <v>7400</v>
-      </c>
       <c r="F27" s="3">
+        <v>7200</v>
+      </c>
+      <c r="G27" s="3">
         <v>243000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>20600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-2700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>43700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>11700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>8900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1875,8 +1933,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1934,8 +1995,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1993,8 +2057,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2052,126 +2119,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-116100</v>
+        <v>54500</v>
       </c>
       <c r="E32" s="3">
-        <v>-60600</v>
+        <v>56000</v>
       </c>
       <c r="F32" s="3">
-        <v>-53500</v>
+        <v>60500</v>
       </c>
       <c r="G32" s="3">
-        <v>-51000</v>
+        <v>51900</v>
       </c>
       <c r="H32" s="3">
-        <v>-50700</v>
+        <v>50800</v>
       </c>
       <c r="I32" s="3">
-        <v>-46800</v>
+        <v>49600</v>
       </c>
       <c r="J32" s="3">
+        <v>46500</v>
+      </c>
+      <c r="K32" s="3">
         <v>-60500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-45500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-139200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-25300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-92000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-37800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-62800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-12100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-48800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-12600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>39900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>32600</v>
+        <v>83700</v>
       </c>
       <c r="E33" s="3">
-        <v>7400</v>
+        <v>108900</v>
       </c>
       <c r="F33" s="3">
-        <v>243000</v>
+        <v>35400</v>
       </c>
       <c r="G33" s="3">
-        <v>11200</v>
+        <v>267400</v>
       </c>
       <c r="H33" s="3">
-        <v>20600</v>
+        <v>43100</v>
       </c>
       <c r="I33" s="3">
-        <v>-2700</v>
+        <v>71700</v>
       </c>
       <c r="J33" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K33" s="3">
         <v>11300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>43700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>8900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2229,131 +2305,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>32600</v>
+        <v>83700</v>
       </c>
       <c r="E35" s="3">
-        <v>7400</v>
+        <v>108900</v>
       </c>
       <c r="F35" s="3">
-        <v>243000</v>
+        <v>35400</v>
       </c>
       <c r="G35" s="3">
-        <v>11200</v>
+        <v>267400</v>
       </c>
       <c r="H35" s="3">
-        <v>20600</v>
+        <v>43100</v>
       </c>
       <c r="I35" s="3">
-        <v>-2700</v>
+        <v>71700</v>
       </c>
       <c r="J35" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K35" s="3">
         <v>11300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>43700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>8900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2375,8 +2460,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2398,72 +2484,76 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>20400</v>
+      </c>
+      <c r="E41" s="3">
         <v>12500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>11700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>132000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>109000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>75100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>51300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -2472,13 +2562,13 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>17800</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -2516,67 +2606,73 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>243200</v>
+        <v>70300</v>
       </c>
       <c r="E43" s="3">
+        <v>99100</v>
+      </c>
+      <c r="F43" s="3">
         <v>209900</v>
       </c>
-      <c r="F43" s="3">
-        <v>215700</v>
-      </c>
       <c r="G43" s="3">
-        <v>230600</v>
+        <v>220400</v>
       </c>
       <c r="H43" s="3">
+        <v>235300</v>
+      </c>
+      <c r="I43" s="3">
         <v>181500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>199000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>204000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>269600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>296200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>262600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>25800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>12000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>13700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2586,327 +2682,342 @@
       <c r="E44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3">
         <v>3100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>9100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>7300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K44" s="3">
+        <v>4800</v>
+      </c>
+      <c r="L44" s="3">
+        <v>13100</v>
+      </c>
+      <c r="M44" s="3">
+        <v>13000</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O44" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P44" s="3">
+        <v>3300</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>3400</v>
+      </c>
+      <c r="R44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="S44" s="3">
+        <v>3600</v>
+      </c>
+      <c r="T44" s="3">
+        <v>3700</v>
+      </c>
+      <c r="U44" s="3">
+        <v>3800</v>
+      </c>
+      <c r="V44" s="3">
         <v>4200</v>
       </c>
-      <c r="J44" s="3">
-        <v>4800</v>
-      </c>
-      <c r="K44" s="3">
-        <v>13100</v>
-      </c>
-      <c r="L44" s="3">
-        <v>13000</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N44" s="3">
-        <v>3000</v>
-      </c>
-      <c r="O44" s="3">
-        <v>3300</v>
-      </c>
-      <c r="P44" s="3">
-        <v>3400</v>
-      </c>
-      <c r="Q44" s="3">
-        <v>3900</v>
-      </c>
-      <c r="R44" s="3">
-        <v>3600</v>
-      </c>
-      <c r="S44" s="3">
-        <v>3700</v>
-      </c>
-      <c r="T44" s="3">
-        <v>3800</v>
-      </c>
-      <c r="U44" s="3">
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>43500</v>
+        <v>156800</v>
       </c>
       <c r="E45" s="3">
-        <v>37700</v>
+        <v>160900</v>
       </c>
       <c r="F45" s="3">
-        <v>34000</v>
+        <v>10300</v>
       </c>
       <c r="G45" s="3">
-        <v>48700</v>
+        <v>3500</v>
       </c>
       <c r="H45" s="3">
-        <v>56800</v>
+        <v>21600</v>
       </c>
       <c r="I45" s="3">
-        <v>41000</v>
+        <v>9900</v>
       </c>
       <c r="J45" s="3">
+        <v>13800</v>
+      </c>
+      <c r="K45" s="3">
         <v>26600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>24300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>27200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>29200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5900</v>
-      </c>
-      <c r="O45" s="3">
-        <v>6000</v>
       </c>
       <c r="P45" s="3">
         <v>6000</v>
       </c>
       <c r="Q45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="R45" s="3">
         <v>7800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>285900</v>
+      </c>
+      <c r="E46" s="3">
         <v>299300</v>
-      </c>
-      <c r="E46" s="3">
-        <v>257300</v>
       </c>
       <c r="F46" s="3">
         <v>257300</v>
       </c>
       <c r="G46" s="3">
+        <v>257300</v>
+      </c>
+      <c r="H46" s="3">
         <v>288500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>247800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>246200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>241900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>318800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>341800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>309500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>166600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>130300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>98200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>76200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>42800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>20400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>20900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>37500</v>
       </c>
     </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2142000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2075900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2526300</v>
       </c>
-      <c r="F47" s="3">
-        <v>2541200</v>
-      </c>
       <c r="G47" s="3">
-        <v>2521700</v>
+        <v>2541000</v>
       </c>
       <c r="H47" s="3">
+        <v>2519200</v>
+      </c>
+      <c r="I47" s="3">
         <v>2490100</v>
       </c>
-      <c r="I47" s="3">
-        <v>2413000</v>
-      </c>
       <c r="J47" s="3">
+        <v>2412900</v>
+      </c>
+      <c r="K47" s="3">
         <v>2381300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2372600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2342300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2361300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1364800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1537900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1554400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1566700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1555200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1524400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1408500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1336800</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3265000</v>
+      </c>
+      <c r="E48" s="3">
         <v>3240200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2774500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2780800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2768500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2750500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2698300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2563800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2563300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2534100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2535100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>187000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>189400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>190800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>193400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>195800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>205300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>207300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>883200</v>
+      </c>
+      <c r="E49" s="3">
         <v>951700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>567900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>596700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>625900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>655000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>681600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>700500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>726900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>751800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>776900</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>8</v>
@@ -2920,8 +3031,8 @@
       <c r="R49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S49" s="3">
-        <v>0</v>
+      <c r="S49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T49" s="3">
         <v>0</v>
@@ -2929,8 +3040,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2988,8 +3102,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3047,67 +3164,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>293100</v>
+        <v>1600</v>
       </c>
       <c r="E52" s="3">
-        <v>321600</v>
+        <v>500</v>
       </c>
       <c r="F52" s="3">
-        <v>320900</v>
+        <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>81500</v>
+        <v>200</v>
       </c>
       <c r="H52" s="3">
-        <v>83500</v>
-      </c>
-      <c r="I52" s="3">
-        <v>85600</v>
+        <v>2400</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J52" s="3">
+        <v>100</v>
+      </c>
+      <c r="K52" s="3">
         <v>32300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>26400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3165,67 +3288,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6860500</v>
+      </c>
+      <c r="E54" s="3">
         <v>6860300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6447600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6496900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6286000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6226900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6124700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5919700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6007200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5996300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6013700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1724700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1865900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1853700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1842600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1799600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1756400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1642200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1588500</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3247,8 +3376,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3270,43 +3400,44 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E57" s="3">
         <v>44500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>34000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>36200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16000</v>
-      </c>
-      <c r="L57" s="3">
-        <v>10900</v>
       </c>
       <c r="M57" s="3">
         <v>10900</v>
       </c>
       <c r="N57" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="O57" s="3">
         <v>0</v>
@@ -3318,42 +3449,45 @@
         <v>0</v>
       </c>
       <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
         <v>18800</v>
       </c>
-      <c r="S57" s="3" t="s">
+      <c r="T57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>200</v>
       </c>
-      <c r="U57" s="3" t="s">
+      <c r="V57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>148800</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
+        <v>179400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>181800</v>
+      </c>
+      <c r="F58" s="3">
+        <v>25000</v>
+      </c>
+      <c r="G58" s="3">
+        <v>29200</v>
+      </c>
+      <c r="H58" s="3">
+        <v>33400</v>
+      </c>
+      <c r="I58" s="3">
+        <v>37800</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>39800</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3362,10 +3496,10 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>54300</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
@@ -3376,8 +3510,8 @@
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3388,161 +3522,170 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>205600</v>
+        <v>44500</v>
       </c>
       <c r="E59" s="3">
-        <v>217500</v>
+        <v>35300</v>
       </c>
       <c r="F59" s="3">
-        <v>216100</v>
+        <v>37300</v>
       </c>
       <c r="G59" s="3">
-        <v>233500</v>
+        <v>28700</v>
       </c>
       <c r="H59" s="3">
-        <v>163100</v>
+        <v>38800</v>
       </c>
       <c r="I59" s="3">
-        <v>230000</v>
+        <v>34200</v>
       </c>
       <c r="J59" s="3">
+        <v>35500</v>
+      </c>
+      <c r="K59" s="3">
         <v>209900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>268700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>295100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>323400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>27500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>25100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>11200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>398700</v>
+      </c>
+      <c r="E60" s="3">
         <v>398900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>234000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>250100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>251100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>199400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>248300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>227800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>284700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>306000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>388600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>25100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>30000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>16500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>12100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3258400</v>
+        <v>3292800</v>
       </c>
       <c r="E61" s="3">
-        <v>3517100</v>
+        <v>3273500</v>
       </c>
       <c r="F61" s="3">
-        <v>3562800</v>
+        <v>3520500</v>
       </c>
       <c r="G61" s="3">
-        <v>3607000</v>
+        <v>3572200</v>
       </c>
       <c r="H61" s="3">
-        <v>3625800</v>
+        <v>3622600</v>
       </c>
       <c r="I61" s="3">
-        <v>3511600</v>
+        <v>3647500</v>
       </c>
       <c r="J61" s="3">
+        <v>3536900</v>
+      </c>
+      <c r="K61" s="3">
         <v>3368500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3447500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2971300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2894000</v>
-      </c>
-      <c r="N61" s="3">
-        <v>657000</v>
       </c>
       <c r="O61" s="3">
         <v>657000</v>
@@ -3554,78 +3697,84 @@
         <v>657000</v>
       </c>
       <c r="R61" s="3">
+        <v>657000</v>
+      </c>
+      <c r="S61" s="3">
         <v>624000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>580000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>493000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>468000</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>120300</v>
+        <v>68600</v>
       </c>
       <c r="E62" s="3">
-        <v>45300</v>
+        <v>66800</v>
       </c>
       <c r="F62" s="3">
-        <v>56900</v>
+        <v>3300</v>
       </c>
       <c r="G62" s="3">
-        <v>57500</v>
+        <v>8600</v>
       </c>
       <c r="H62" s="3">
-        <v>64900</v>
+        <v>3700</v>
       </c>
       <c r="I62" s="3">
-        <v>90000</v>
+        <v>7000</v>
       </c>
       <c r="J62" s="3">
+        <v>31400</v>
+      </c>
+      <c r="K62" s="3">
         <v>50700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>47700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>85800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>222700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>135300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>193700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>197500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>227500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>208600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>247800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>243500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>232300</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3683,8 +3832,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3742,8 +3894,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3801,67 +3956,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>8067200</v>
+        <v>3798000</v>
       </c>
       <c r="E66" s="3">
-        <v>7421000</v>
+        <v>3777600</v>
       </c>
       <c r="F66" s="3">
-        <v>7027700</v>
+        <v>3796400</v>
       </c>
       <c r="G66" s="3">
-        <v>7124000</v>
+        <v>3869900</v>
       </c>
       <c r="H66" s="3">
-        <v>7132700</v>
+        <v>3915500</v>
       </c>
       <c r="I66" s="3">
-        <v>6760900</v>
+        <v>3890100</v>
       </c>
       <c r="J66" s="3">
+        <v>3850000</v>
+      </c>
+      <c r="K66" s="3">
         <v>6759500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6841700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7177700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7151500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2301900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2350100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2359900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2173600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2046100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1683600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1571900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1518000</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3883,8 +4044,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3942,8 +4104,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4001,8 +4166,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4060,8 +4228,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4119,67 +4290,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1720700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1206900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-973500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-723500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-929800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-902400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-863500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-958600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-941700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1181300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1137900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-577300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-484100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-506200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-369300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-391000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-400400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-402700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-402500</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4237,8 +4414,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4296,8 +4476,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4355,67 +4538,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1720700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1206900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-973400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-530800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-838000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-905800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-636200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-839800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-834600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-1181300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-1137900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-577200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-484100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-506200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-331000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-246500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>72800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>70300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4473,131 +4662,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>32600</v>
+        <v>83700</v>
       </c>
       <c r="E81" s="3">
-        <v>7400</v>
+        <v>108900</v>
       </c>
       <c r="F81" s="3">
-        <v>243000</v>
+        <v>35400</v>
       </c>
       <c r="G81" s="3">
-        <v>11200</v>
+        <v>267400</v>
       </c>
       <c r="H81" s="3">
-        <v>20600</v>
+        <v>43100</v>
       </c>
       <c r="I81" s="3">
-        <v>-2700</v>
+        <v>71700</v>
       </c>
       <c r="J81" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K81" s="3">
         <v>11300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>43700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>8900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4619,49 +4817,50 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>75100</v>
+        <v>39400</v>
       </c>
       <c r="E83" s="3">
-        <v>73600</v>
+        <v>38900</v>
       </c>
       <c r="F83" s="3">
-        <v>72700</v>
+        <v>38400</v>
       </c>
       <c r="G83" s="3">
-        <v>69900</v>
+        <v>37200</v>
       </c>
       <c r="H83" s="3">
-        <v>69500</v>
+        <v>34900</v>
       </c>
       <c r="I83" s="3">
-        <v>68900</v>
+        <v>36700</v>
       </c>
       <c r="J83" s="3">
+        <v>30800</v>
+      </c>
+      <c r="K83" s="3">
         <v>67700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>65000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>66600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>61000</v>
-      </c>
-      <c r="N83" s="3">
-        <v>4100</v>
       </c>
       <c r="O83" s="3">
         <v>4100</v>
       </c>
       <c r="P83" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="Q83" s="3">
         <v>4000</v>
@@ -4673,13 +4872,16 @@
         <v>4000</v>
       </c>
       <c r="T83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="U83" s="3">
         <v>8000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4737,8 +4939,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4796,8 +5001,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4855,8 +5063,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4914,8 +5125,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4973,67 +5187,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>214100</v>
+      </c>
+      <c r="E89" s="3">
         <v>125500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>153700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>178900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>174500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>111500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>119600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>159800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>184300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>170500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>98400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>51300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>57300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>57800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>43300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>26800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>50700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>86800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5055,67 +5275,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-39900</v>
+        <v>-58500</v>
       </c>
       <c r="E91" s="3">
-        <v>-60200</v>
+        <v>-39400</v>
       </c>
       <c r="F91" s="3">
-        <v>-68700</v>
+        <v>-58000</v>
       </c>
       <c r="G91" s="3">
-        <v>-86800</v>
+        <v>-67100</v>
       </c>
       <c r="H91" s="3">
-        <v>-105500</v>
+        <v>-85600</v>
       </c>
       <c r="I91" s="3">
-        <v>-68600</v>
+        <v>-101300</v>
       </c>
       <c r="J91" s="3">
+        <v>-58900</v>
+      </c>
+      <c r="K91" s="3">
         <v>-47800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-93900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-47200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-32800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-26500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5173,8 +5397,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5232,67 +5459,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-109200</v>
+      </c>
+      <c r="E94" s="3">
         <v>105300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-62000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-103700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-134700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-201400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-246500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-69700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-147400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-49700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-19400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>7600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>12500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-37100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-126000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-175300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-97600</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5314,43 +5547,44 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-70500</v>
+        <v>118200</v>
       </c>
       <c r="E96" s="3">
-        <v>-700</v>
+        <v>116000</v>
       </c>
       <c r="F96" s="3">
-        <v>-200</v>
+        <v>38700</v>
       </c>
       <c r="G96" s="3">
-        <v>-200</v>
+        <v>23500</v>
       </c>
       <c r="H96" s="3">
-        <v>-200</v>
+        <v>22000</v>
       </c>
       <c r="I96" s="3">
-        <v>-200</v>
+        <v>19600</v>
       </c>
       <c r="J96" s="3">
+        <v>16900</v>
+      </c>
+      <c r="K96" s="3">
         <v>-300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
       <c r="N96" s="3">
-        <v>-5600</v>
+        <v>0</v>
       </c>
       <c r="O96" s="3">
         <v>-5600</v>
@@ -5362,7 +5596,7 @@
         <v>-5600</v>
       </c>
       <c r="R96" s="3">
-        <v>0</v>
+        <v>-5600</v>
       </c>
       <c r="S96" s="3">
         <v>0</v>
@@ -5373,8 +5607,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5432,8 +5669,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5491,8 +5731,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5550,43 +5793,46 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-97000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-228000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-86500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-70700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-42000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>90200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>122500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-95400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-30600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-133200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-80100</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-35900</v>
       </c>
       <c r="O100" s="3">
         <v>-35900</v>
@@ -5595,45 +5841,48 @@
         <v>-35900</v>
       </c>
       <c r="Q100" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="R100" s="3">
         <v>-2900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>32400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>75400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>84400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5668,63 +5917,69 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E102" s="3">
         <v>2800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>23000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>33900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>23800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>27100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>22200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>KNTK</t>
   </si>
@@ -656,289 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>385700</v>
+      </c>
+      <c r="E8" s="3">
         <v>396400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>359500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>341400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>348900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>330300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>296200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>281000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>295500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>325200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>335600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>257200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>56300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>34500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>35600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>34100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>35300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>40200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>73000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>229900</v>
+      </c>
+      <c r="E9" s="3">
         <v>199000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>190600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>197100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>184300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>190700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>150400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>151900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>124400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>151100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>158600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>124400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>20600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>9600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>10700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>19100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>18900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>40200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>155800</v>
+      </c>
+      <c r="E10" s="3">
         <v>197400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>168900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>144300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>164500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>139600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>145800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>129200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>171100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>174100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>177000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>132800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>35700</v>
-      </c>
-      <c r="P10" s="3">
-        <v>24900</v>
       </c>
       <c r="Q10" s="3">
         <v>24900</v>
       </c>
       <c r="R10" s="3">
+        <v>24900</v>
+      </c>
+      <c r="S10" s="3">
         <v>24700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>16200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>21300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>32800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1023,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,114 +1101,120 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-28600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-56200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>4200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>7700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>12100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>400</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>22900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-4500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>160400</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1600</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E15" s="3">
         <v>87600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>75100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>73600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>72700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>69900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>69500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>68900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>67700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>65000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>66600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>61000</v>
-      </c>
-      <c r="O15" s="3">
-        <v>4100</v>
       </c>
       <c r="P15" s="3">
         <v>4100</v>
       </c>
       <c r="Q15" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="R15" s="3">
         <v>4000</v>
@@ -1204,13 +1226,16 @@
         <v>4000</v>
       </c>
       <c r="U15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="V15" s="3">
         <v>8000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>355700</v>
+      </c>
+      <c r="E17" s="3">
         <v>322100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>299700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>311100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>286900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>289000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>246600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>253400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>250500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>279400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>317800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>233700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>192400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>20000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>22000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>23000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>42500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E18" s="3">
         <v>74300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>59700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>30300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>61900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>41300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>49600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>27600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>45000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>45800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>23500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-136100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>19000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>30500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,295 +1410,308 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-54500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-56000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-60500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-51900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-50800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-49600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-46500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>60500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>45500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>139200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>25300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>92000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>37800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>62800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>12100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>48800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>12600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-39900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-44500</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>160700</v>
+      </c>
+      <c r="E21" s="3">
         <v>216400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>190800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>164300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>186500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>162000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>168700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>143000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>173200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>156300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>223500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>109900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-40000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>56400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>80500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>29100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>65000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>35600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-21900</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E22" s="3">
         <v>66000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>54000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>47500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>75400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>45000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>16100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>69300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>56700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>40500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>25300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>26800</v>
-      </c>
-      <c r="O22" s="3">
-        <v>2700</v>
       </c>
       <c r="P22" s="3">
         <v>2700</v>
       </c>
       <c r="Q22" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="R22" s="3">
         <v>2600</v>
       </c>
       <c r="S22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="T22" s="3">
         <v>1200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E23" s="3">
         <v>91900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>118200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>39200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>32400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>44400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>72000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>48800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>50800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>131600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>22100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-46800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>49700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>73800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>22500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>59800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>31200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-10000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E24" s="3">
         <v>8300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-234900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>400</v>
       </c>
       <c r="K24" s="3">
         <v>400</v>
       </c>
       <c r="L24" s="3">
+        <v>400</v>
+      </c>
+      <c r="M24" s="3">
         <v>1400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
@@ -1683,13 +1728,16 @@
         <v>0</v>
       </c>
       <c r="U24" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="V24" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E26" s="3">
         <v>83700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>108900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>35400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>267400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>43100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>71700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>48500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>49400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>131400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-46800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>49700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>73800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>22500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>59800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>31200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-25400</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>300</v>
+      </c>
+      <c r="E27" s="3">
         <v>21000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>32600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>243000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-2700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>43700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-31000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>8900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1998,8 +2058,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E32" s="3">
         <v>54500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>56000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>60500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>51900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>50800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>49600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>46500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-60500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-45500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-139200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-25300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-92000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-37800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-62800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-12100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-48800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-12600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>39900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E33" s="3">
         <v>83700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>108900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>35400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>267400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>43100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>71700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>43700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-31000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>8900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E35" s="3">
         <v>83700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>108900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>35400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>267400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>43100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>71700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>43700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-31000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>8900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,94 +2570,98 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E41" s="3">
         <v>20400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>17600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>132000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>109000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>75100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>51300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>500</v>
+      </c>
+      <c r="E42" s="3">
         <v>100</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>4300</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>17800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -2609,75 +2698,81 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>116600</v>
+      </c>
+      <c r="E43" s="3">
         <v>70300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>99100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>209900</v>
       </c>
-      <c r="G43" s="3">
-        <v>220400</v>
-      </c>
       <c r="H43" s="3">
+        <v>215700</v>
+      </c>
+      <c r="I43" s="3">
         <v>235300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>181500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>199000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>204000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>269600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>296200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>262600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>25800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>12000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>13700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>12900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>13600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>8</v>
+      <c r="D44" s="3">
+        <v>3600</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>8</v>
@@ -2685,342 +2780,357 @@
       <c r="F44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3">
         <v>3100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>9100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>7300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>4700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13000</v>
       </c>
-      <c r="N44" s="3" t="s">
+      <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>142300</v>
+      </c>
+      <c r="E45" s="3">
         <v>156800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>160900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>10300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>24300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>29200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5900</v>
-      </c>
-      <c r="P45" s="3">
-        <v>6000</v>
       </c>
       <c r="Q45" s="3">
         <v>6000</v>
       </c>
       <c r="R45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="S45" s="3">
         <v>7800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>294800</v>
+      </c>
+      <c r="E46" s="3">
         <v>285900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>299300</v>
-      </c>
-      <c r="F46" s="3">
-        <v>257300</v>
       </c>
       <c r="G46" s="3">
         <v>257300</v>
       </c>
       <c r="H46" s="3">
+        <v>257300</v>
+      </c>
+      <c r="I46" s="3">
         <v>288500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>247800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>246200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>241900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>318800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>341800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>309500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>166600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>130300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>98200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>76200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>42800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>20400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>20900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>37500</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2117900</v>
+      </c>
+      <c r="E47" s="3">
         <v>2142000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2075900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2526300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2541000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2519200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2490100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2412900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2381300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2372600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2342300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2361300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1364800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1537900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1554400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1566700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1555200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1524400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1408500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1336800</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3463700</v>
+      </c>
+      <c r="E48" s="3">
         <v>3265000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3240200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2774500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2780800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2768500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2750500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2698300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2563800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2563300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2534100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2535100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>187000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>189400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>190800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>193400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>195800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>205300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>207300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>657600</v>
+      </c>
+      <c r="E49" s="3">
         <v>883200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>951700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>567900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>596700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>625900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>655000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>681600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>700500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>726900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>751800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>776900</v>
-      </c>
-      <c r="O49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>8</v>
@@ -3034,8 +3144,8 @@
       <c r="S49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T49" s="3">
-        <v>0</v>
+      <c r="T49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U49" s="3">
         <v>0</v>
@@ -3043,8 +3153,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,70 +3283,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>100</v>
+      </c>
+      <c r="E52" s="3">
         <v>1600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2400</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>32300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>26400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>30900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6814900</v>
+      </c>
+      <c r="E54" s="3">
         <v>6860500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6860300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6447600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6496900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6286000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6226900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6124700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5919700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6007200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5996300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6013700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1724700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1865900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1853700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1842600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1799600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1756400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1642200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1588500</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,46 +3530,47 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E57" s="3">
         <v>17200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>44500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>34000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>36200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16000</v>
-      </c>
-      <c r="M57" s="3">
-        <v>10900</v>
       </c>
       <c r="N57" s="3">
         <v>10900</v>
       </c>
       <c r="O57" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="P57" s="3">
         <v>0</v>
@@ -3452,46 +3582,49 @@
         <v>0</v>
       </c>
       <c r="S57" s="3">
+        <v>0</v>
+      </c>
+      <c r="T57" s="3">
         <v>18800</v>
       </c>
-      <c r="T57" s="3" t="s">
+      <c r="U57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>200</v>
       </c>
-      <c r="V57" s="3" t="s">
+      <c r="W57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>160100</v>
+      </c>
+      <c r="E58" s="3">
         <v>179400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>181800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>25000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>29200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>33400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>37800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>39800</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -3499,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>54300</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
@@ -3513,8 +3646,8 @@
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -3525,170 +3658,179 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>73500</v>
+      </c>
+      <c r="E59" s="3">
         <v>44500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>35300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>37300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>28700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>38800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>34200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>35500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>209900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>268700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>295100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>323400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>27200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>27500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>25100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>11200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>418600</v>
+      </c>
+      <c r="E60" s="3">
         <v>398700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>398900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>234000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>250100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>251100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>199400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>248300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>227800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>284700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>306000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>388600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>27200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>27500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>25100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>21900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>30000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>16500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>12100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3375500</v>
+      </c>
+      <c r="E61" s="3">
         <v>3292800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3273500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3520500</v>
       </c>
-      <c r="G61" s="3">
-        <v>3572200</v>
-      </c>
       <c r="H61" s="3">
+        <v>3577500</v>
+      </c>
+      <c r="I61" s="3">
         <v>3622600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3647500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3536900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3368500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3447500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2971300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2894000</v>
-      </c>
-      <c r="O61" s="3">
-        <v>657000</v>
       </c>
       <c r="P61" s="3">
         <v>657000</v>
@@ -3700,81 +3842,87 @@
         <v>657000</v>
       </c>
       <c r="S61" s="3">
+        <v>657000</v>
+      </c>
+      <c r="T61" s="3">
         <v>624000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>580000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>493000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>468000</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E62" s="3">
         <v>68600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>66800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3300</v>
       </c>
-      <c r="G62" s="3">
-        <v>8600</v>
-      </c>
       <c r="H62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="I62" s="3">
         <v>3700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>7000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>31400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>50700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>47700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>85800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>222700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>135300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>193700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>197500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>227500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>208600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>247800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>243500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>232300</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3835900</v>
+      </c>
+      <c r="E66" s="3">
         <v>3798000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3777600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3796400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3869900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3915500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3890100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3850000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6759500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6841700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7177700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7151500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2301900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2350100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2359900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2173600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2046100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1683600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1571900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1518000</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4231,8 +4398,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2976600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1720700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1206900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-973500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-723500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-929800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-902400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-863500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-958600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-941700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1181300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1137900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-577300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-484100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-506200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-369300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-391000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-400400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-402700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-402500</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2976600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1720700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1206900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-973400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-530800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-838000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-905800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-636200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-839800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-834600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-1181300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-1137900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-577200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-484100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-506200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-331000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-246500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>72800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>70300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E81" s="3">
         <v>83700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>108900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>35400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>267400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>43100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>71700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>43700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-31000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>8900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,52 +5015,53 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E83" s="3">
         <v>39400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>38900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>38400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>37200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>34900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>36700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>30800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>67700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>65000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>66600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>61000</v>
-      </c>
-      <c r="O83" s="3">
-        <v>4100</v>
       </c>
       <c r="P83" s="3">
         <v>4100</v>
       </c>
       <c r="Q83" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="R83" s="3">
         <v>4000</v>
@@ -4875,13 +5073,16 @@
         <v>4000</v>
       </c>
       <c r="U83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="V83" s="3">
         <v>8000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E89" s="3">
         <v>214100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>125500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>153700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>178900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>174500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>111500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>119600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>159800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>184300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>170500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>98400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>51300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>57300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>57800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>43300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>26800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>50700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>86800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,70 +5495,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-107700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-58500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-39400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-58000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-67100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-85600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-101300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-58900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-47800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-93900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-47200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-32800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-26500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-111000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-109200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>105300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-62000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-103700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-134700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-201400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-246500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-69700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-147400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-49700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-19400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>7600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>12500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>1900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-13200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-37100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-126000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-175300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-97600</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,46 +5780,47 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E96" s="3">
         <v>118200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>116000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>38700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>23500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>22000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>19600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>16900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
       <c r="O96" s="3">
-        <v>-5600</v>
+        <v>0</v>
       </c>
       <c r="P96" s="3">
         <v>-5600</v>
@@ -5599,7 +5832,7 @@
         <v>-5600</v>
       </c>
       <c r="S96" s="3">
-        <v>0</v>
+        <v>-5600</v>
       </c>
       <c r="T96" s="3">
         <v>0</v>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,46 +6038,49 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-49800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-97000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-228000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-86500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-70700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-42000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>90200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>122500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-95400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-30600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-133200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-80100</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-35900</v>
       </c>
       <c r="P100" s="3">
         <v>-35900</v>
@@ -5844,22 +6089,25 @@
         <v>-35900</v>
       </c>
       <c r="R100" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="S100" s="3">
         <v>-2900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>32400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>75400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>84400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5884,8 +6132,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -5920,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E102" s="3">
         <v>7900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>4400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>23000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>33900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>23800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>27100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>22200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>KNTK</t>
   </si>
@@ -656,301 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>443300</v>
+      </c>
+      <c r="E8" s="3">
         <v>385700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>396400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>359500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>341400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>348900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>330300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>296200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>281000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>295500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>325200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>335600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>257200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>56300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>34500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>35600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>34100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>35300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>40200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>73000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>287000</v>
+      </c>
+      <c r="E9" s="3">
         <v>229900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>199000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>190600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>197100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>184300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>190700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>150400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>151900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>124400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>151100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>158600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>124400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>20600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>9600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>10700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>9400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>19100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>18900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>40200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>156300</v>
+      </c>
+      <c r="E10" s="3">
         <v>155800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>197400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>168900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>144300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>164500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>139600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>145800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>129200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>171100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>174100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>177000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>132800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>35700</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>24900</v>
       </c>
       <c r="R10" s="3">
         <v>24900</v>
       </c>
       <c r="S10" s="3">
+        <v>24900</v>
+      </c>
+      <c r="T10" s="3">
         <v>24700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>16200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>21300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>32800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,120 +1121,126 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>6400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-28600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-56200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>12100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>22900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-4500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>160400</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1600</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>92700</v>
+      </c>
+      <c r="E15" s="3">
         <v>87900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>87600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>75100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>73600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>72700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>69900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>69500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>68900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>67700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>65000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>66600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>61000</v>
-      </c>
-      <c r="P15" s="3">
-        <v>4100</v>
       </c>
       <c r="Q15" s="3">
         <v>4100</v>
       </c>
       <c r="R15" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="S15" s="3">
         <v>4000</v>
@@ -1229,13 +1252,16 @@
         <v>4000</v>
       </c>
       <c r="V15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W15" s="3">
         <v>8000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>424000</v>
+      </c>
+      <c r="E17" s="3">
         <v>355700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>322100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>299700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>311100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>286900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>289000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>246600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>253400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>250500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>279400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>317800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>233700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>192400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>22000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>23000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>21200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>42500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E18" s="3">
         <v>30000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>74300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>59700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>30300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>61900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>41300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>49600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>45000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>45800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>23500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-136100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>19000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>30500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,310 +1444,323 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-57500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-42700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-54500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-56000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-60500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-51900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-50800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-49600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-46500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>60500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>45500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>139200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>25300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>92000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>37800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>62800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>12100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>48800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>12600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-39900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-44500</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>169400</v>
+      </c>
+      <c r="E21" s="3">
         <v>160700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>216400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>190800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>164300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>186500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>162000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>168700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>143000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>173200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>156300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>223500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>109900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-40000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>56400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>80500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>29100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>65000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>35600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-21900</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>55700</v>
+      </c>
+      <c r="E22" s="3">
         <v>49700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>66000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>54000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>47500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>75400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>45000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>16100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>69300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>56700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>40500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>25300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>26800</v>
-      </c>
-      <c r="P22" s="3">
-        <v>2700</v>
       </c>
       <c r="Q22" s="3">
         <v>2700</v>
       </c>
       <c r="R22" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="S22" s="3">
         <v>2600</v>
       </c>
       <c r="T22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="U22" s="3">
         <v>1200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E23" s="3">
         <v>18000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>91900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>118200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>39200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>32400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>44400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>72000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>48800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>50800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>131600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>22100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-46800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>49700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>73800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>22500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>59800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>31200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-234900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>300</v>
-      </c>
-      <c r="K24" s="3">
-        <v>400</v>
       </c>
       <c r="L24" s="3">
         <v>400</v>
       </c>
       <c r="M24" s="3">
+        <v>400</v>
+      </c>
+      <c r="N24" s="3">
         <v>1400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
@@ -1731,13 +1777,16 @@
         <v>0</v>
       </c>
       <c r="V24" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="W24" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E26" s="3">
         <v>16200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>83700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>108900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>35400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>267400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>43100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>71700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>48500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>49400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>131400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>21400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-46800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>49700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>73800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>22500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>59800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>31200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-9300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-25400</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E27" s="3">
         <v>300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>32600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>243000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>20600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-2700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>43700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>11700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-9000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2061,8 +2122,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>57500</v>
+      </c>
+      <c r="E32" s="3">
         <v>42700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>54500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>56000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>60500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>51900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>50800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>49600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>46500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-60500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-45500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-139200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-25300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-92000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-37800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-62800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-12100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-48800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-12600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>39900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E33" s="3">
         <v>16200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>83700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>108900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>35400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>267400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>43100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>71700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>43700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>11700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>8900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-9000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E35" s="3">
         <v>16200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>83700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>108900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>35400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>267400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>43100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>71700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>43700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>11700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>8900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-9000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,73 +2657,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E41" s="3">
         <v>3600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>132000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>109000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>75100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>51300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>24200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2645,26 +2735,26 @@
         <v>500</v>
       </c>
       <c r="E42" s="3">
+        <v>500</v>
+      </c>
+      <c r="F42" s="3">
         <v>100</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>4300</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>17800</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2701,81 +2791,87 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>122500</v>
+      </c>
+      <c r="E43" s="3">
         <v>116600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>70300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>99100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>209900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>215700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>235300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>181500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>199000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>204000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>269600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>296200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>262600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>25800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>12000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>13700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>13700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>13600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>3600</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>8</v>
@@ -2783,357 +2879,372 @@
       <c r="G44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3">
         <v>3100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>4700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13000</v>
       </c>
-      <c r="O44" s="3" t="s">
+      <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>150600</v>
+      </c>
+      <c r="E45" s="3">
         <v>142300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>156800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>160900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>26600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>24300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>29200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5900</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>6000</v>
       </c>
       <c r="R45" s="3">
         <v>6000</v>
       </c>
       <c r="S45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="T45" s="3">
         <v>7800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>315000</v>
+      </c>
+      <c r="E46" s="3">
         <v>294800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>285900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>299300</v>
-      </c>
-      <c r="G46" s="3">
-        <v>257300</v>
       </c>
       <c r="H46" s="3">
         <v>257300</v>
       </c>
       <c r="I46" s="3">
+        <v>257300</v>
+      </c>
+      <c r="J46" s="3">
         <v>288500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>247800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>246200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>241900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>318800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>341800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>309500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>166600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>130300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>98200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>76200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>42800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>20400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>20900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>37500</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2112300</v>
+      </c>
+      <c r="E47" s="3">
         <v>2117900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2142000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2075900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2526300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2541000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2519200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2490100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2412900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2381300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2372600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2342300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2361300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1364800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1537900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1554400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1566700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1555200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1524400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1408500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1336800</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3675900</v>
+      </c>
+      <c r="E48" s="3">
         <v>3463700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3265000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3240200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2774500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2780800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2768500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2750500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2698300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2563800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2563300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2534100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2535100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>187000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>189400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>190800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>193400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>195800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>205300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>207300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>638900</v>
+      </c>
+      <c r="E49" s="3">
         <v>657600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>883200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>951700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>567900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>596700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>625900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>655000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>681600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>700500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>726900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>751800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>776900</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>8</v>
@@ -3147,8 +3258,8 @@
       <c r="T49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U49" s="3">
-        <v>0</v>
+      <c r="U49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V49" s="3">
         <v>0</v>
@@ -3156,8 +3267,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,8 +3403,11 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3295,64 +3415,67 @@
         <v>100</v>
       </c>
       <c r="E52" s="3">
+        <v>100</v>
+      </c>
+      <c r="F52" s="3">
         <v>1600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2400</v>
       </c>
-      <c r="J52" s="3" t="s">
+      <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>32300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>26400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>30900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7030700</v>
+      </c>
+      <c r="E54" s="3">
         <v>6814900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6860500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6860300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6447600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6496900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6286000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6226900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6124700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5919700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6007200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5996300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6013700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1724700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1865900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1853700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1842600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1799600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1756400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1642200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1588500</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,49 +3661,50 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E57" s="3">
         <v>27200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>44500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>34000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>36200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16000</v>
-      </c>
-      <c r="N57" s="3">
-        <v>10900</v>
       </c>
       <c r="O57" s="3">
         <v>10900</v>
       </c>
       <c r="P57" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -3585,49 +3716,52 @@
         <v>0</v>
       </c>
       <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
         <v>18800</v>
       </c>
-      <c r="U57" s="3" t="s">
+      <c r="V57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>200</v>
       </c>
-      <c r="W57" s="3" t="s">
+      <c r="X57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>165100</v>
+      </c>
+      <c r="E58" s="3">
         <v>160100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>179400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>181800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>25000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>29200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>33400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>37800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>39800</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -3635,10 +3769,10 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>54300</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>8</v>
@@ -3649,8 +3783,8 @@
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U58" s="3">
         <v>0</v>
@@ -3661,179 +3795,188 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E59" s="3">
         <v>73500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>44500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>35300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>37300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>28700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>38800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>34200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>35500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>209900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>268700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>295100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>323400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>27200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>27500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>25100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>21900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>11200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>11900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>475300</v>
+      </c>
+      <c r="E60" s="3">
         <v>418600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>398700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>398900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>234000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>250100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>251100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>199400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>248300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>227800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>284700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>306000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>388600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>27200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>25100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>21900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>30000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>16500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>12100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3588600</v>
+      </c>
+      <c r="E61" s="3">
         <v>3375500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3292800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3273500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3520500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3577500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3622600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3647500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3536900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3368500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3447500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2971300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2894000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>657000</v>
       </c>
       <c r="Q61" s="3">
         <v>657000</v>
@@ -3845,84 +3988,90 @@
         <v>657000</v>
       </c>
       <c r="T61" s="3">
+        <v>657000</v>
+      </c>
+      <c r="U61" s="3">
         <v>624000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>580000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>493000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>468000</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E62" s="3">
         <v>4100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>68600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>66800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>7000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>31400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>50700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>47700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>85800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>222700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>135300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>193700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>197500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>227500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>208600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>247800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>243500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>232300</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4129800</v>
+      </c>
+      <c r="E66" s="3">
         <v>3835900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3798000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3777600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3796400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3869900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3915500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3890100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3850000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6759500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6841700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7177700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7151500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2301900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2350100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2359900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2173600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2046100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1683600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1571900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1518000</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4401,8 +4569,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2616600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2976600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1720700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1206900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-973500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-723500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-929800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-902400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-863500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-958600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-941700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1181300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1137900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-577300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-484100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-506200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-369300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-391000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-400400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-402700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-402500</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2549700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2976600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1720700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1206900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-973400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-530800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-838000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-905800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-636200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-839800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-834600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-1181300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-1137900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-577200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-484100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-506200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-331000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-246500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>72800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>70300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E81" s="3">
         <v>16200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>83700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>108900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>35400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>267400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>43100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>71700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>43700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-31000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>11700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>8900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-9000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,55 +5214,56 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E83" s="3">
         <v>42000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>39400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>38900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>38400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>37200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>34900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>36700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>30800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>67700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>65000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>66600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>61000</v>
-      </c>
-      <c r="P83" s="3">
-        <v>4100</v>
       </c>
       <c r="Q83" s="3">
         <v>4100</v>
       </c>
       <c r="R83" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="S83" s="3">
         <v>4000</v>
@@ -5076,13 +5275,16 @@
         <v>4000</v>
       </c>
       <c r="V83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="W83" s="3">
         <v>8000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>176800</v>
+      </c>
+      <c r="E89" s="3">
         <v>144000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>214100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>125500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>153700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>178900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>174500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>111500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>119600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>159800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>184300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>170500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>98400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>51300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>57300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>57800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>43300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>26800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>50700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>86800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-74500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-107700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-58500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-39400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-58000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-67100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-85600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-101300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-58900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-47800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-93900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-47200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-32800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-26500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-260100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-111000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-109200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>105300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-62000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-103700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-134700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-201400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-246500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-69700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-147400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-49700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-19400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>7600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>12500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>1900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-13200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-37100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-126000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-175300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-97600</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,49 +6014,50 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>123200</v>
+      </c>
+      <c r="E96" s="3">
         <v>123000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>118200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>116000</v>
       </c>
-      <c r="G96" s="3">
-        <v>38700</v>
-      </c>
       <c r="H96" s="3">
+        <v>39500</v>
+      </c>
+      <c r="I96" s="3">
         <v>23500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>22000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>19600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>16900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-400</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
-        <v>-5600</v>
+        <v>0</v>
       </c>
       <c r="Q96" s="3">
         <v>-5600</v>
@@ -5835,7 +6069,7 @@
         <v>-5600</v>
       </c>
       <c r="T96" s="3">
-        <v>0</v>
+        <v>-5600</v>
       </c>
       <c r="U96" s="3">
         <v>0</v>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,49 +6284,52 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-49800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-97000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-228000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-86500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-70700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-42000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>90200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>122500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-95400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-30600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-133200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-80100</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-35900</v>
       </c>
       <c r="Q100" s="3">
         <v>-35900</v>
@@ -6092,22 +6338,25 @@
         <v>-35900</v>
       </c>
       <c r="S100" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="T100" s="3">
         <v>-2900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>32400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>75400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>84400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6135,8 +6384,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6171,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>4400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>23000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>33900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>23800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>27100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>22200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="92">
   <si>
     <t>KNTK</t>
   </si>
@@ -656,314 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>426700</v>
+      </c>
+      <c r="E8" s="3">
         <v>443300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>385700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>396400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>359500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>341400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>348900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>330300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>296200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>281000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>295500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>325200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>335600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>257200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>56300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>34500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>35600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>35300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>40200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>73000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>224700</v>
+      </c>
+      <c r="E9" s="3">
         <v>287000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>229900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>199000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>190600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>197100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>184300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>190700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>150400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>151900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>124400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>151100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>158600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>124400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>20600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>9600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>10700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>19100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>18900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>40200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>202000</v>
+      </c>
+      <c r="E10" s="3">
         <v>156300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>155800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>197400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>168900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>144300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>164500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>139600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>145800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>129200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>171100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>174100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>177000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>132800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>35700</v>
-      </c>
-      <c r="R10" s="3">
-        <v>24900</v>
       </c>
       <c r="S10" s="3">
         <v>24900</v>
       </c>
       <c r="T10" s="3">
+        <v>24900</v>
+      </c>
+      <c r="U10" s="3">
         <v>24700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>16200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>21300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>32800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,126 +1141,132 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>6400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-28600</v>
       </c>
-      <c r="G14" s="3">
-        <v>-56200</v>
-      </c>
       <c r="H14" s="3">
+        <v>-59400</v>
+      </c>
+      <c r="I14" s="3">
         <v>4200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>12100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>22900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>160400</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1600</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>93800</v>
+      </c>
+      <c r="E15" s="3">
         <v>92700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>87900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>87600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>75100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>73600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>72700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>69900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>69500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>68900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>67700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>65000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>66600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>61000</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>4100</v>
       </c>
       <c r="R15" s="3">
         <v>4100</v>
       </c>
       <c r="S15" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="T15" s="3">
         <v>4000</v>
@@ -1255,13 +1278,16 @@
         <v>4000</v>
       </c>
       <c r="W15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="X15" s="3">
         <v>8000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>349300</v>
+      </c>
+      <c r="E17" s="3">
         <v>424000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>355700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>322100</v>
       </c>
-      <c r="G17" s="3">
-        <v>299700</v>
-      </c>
       <c r="H17" s="3">
+        <v>302900</v>
+      </c>
+      <c r="I17" s="3">
         <v>311100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>286900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>289000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>246600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>253400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>250500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>279400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>317800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>233700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>192400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>20000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>23000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>42500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>77400</v>
+      </c>
+      <c r="E18" s="3">
         <v>19200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>30000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>74300</v>
       </c>
-      <c r="G18" s="3">
-        <v>59700</v>
-      </c>
       <c r="H18" s="3">
+        <v>56500</v>
+      </c>
+      <c r="I18" s="3">
         <v>30300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>61900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>41300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>49600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>27600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>45000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>45800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>23500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-136100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>14500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>13600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>12300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>19000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>30500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,325 +1478,338 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-61100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-57500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-42700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-54500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-56000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-60500</v>
-      </c>
       <c r="I20" s="3">
+        <v>-60000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-51900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-50800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-49600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-46500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>60500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>45500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>139200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>25300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>92000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>37800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>62800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>12100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>48800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>12600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-39900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-44500</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>232300</v>
+      </c>
+      <c r="E21" s="3">
         <v>169400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>160700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>216400</v>
       </c>
-      <c r="G21" s="3">
-        <v>190800</v>
-      </c>
       <c r="H21" s="3">
-        <v>164300</v>
+        <v>187500</v>
       </c>
       <c r="I21" s="3">
+        <v>163900</v>
+      </c>
+      <c r="J21" s="3">
         <v>186500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>162000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>168700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>143000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>173200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>156300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>223500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>109900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-40000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>56400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>80500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>29100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>65000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>35600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-1500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-21900</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E22" s="3">
         <v>55700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>49700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>66000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>54000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>47500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>75400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>45000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>16100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>69300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>56700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>40500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>25300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>26800</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>2700</v>
       </c>
       <c r="R22" s="3">
         <v>2700</v>
       </c>
       <c r="S22" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="T22" s="3">
         <v>2600</v>
       </c>
       <c r="U22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="V22" s="3">
         <v>1200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>81700</v>
+      </c>
+      <c r="E23" s="3">
         <v>21800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>91900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>118200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>39200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>32400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>44400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>72000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>48800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>50800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>131600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>22100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-46800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>49700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>73800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>22500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>59800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>31200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E24" s="3">
         <v>2600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-234900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>300</v>
-      </c>
-      <c r="L24" s="3">
-        <v>400</v>
       </c>
       <c r="M24" s="3">
         <v>400</v>
       </c>
       <c r="N24" s="3">
+        <v>400</v>
+      </c>
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
@@ -1780,13 +1826,16 @@
         <v>0</v>
       </c>
       <c r="W24" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="X24" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E26" s="3">
         <v>19300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>83700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>108900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>35400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>267400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>43100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>71700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>48500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>49400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>131400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>21400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-46800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>49700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>73800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>22500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>59800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>31200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-9300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-25400</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E27" s="3">
         <v>2800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>21000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>32600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>243000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>20600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>43700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-31000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>11700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>8900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-9000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2328,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>61100</v>
+      </c>
+      <c r="E32" s="3">
         <v>57500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>42700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>54500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>56000</v>
       </c>
-      <c r="H32" s="3">
-        <v>60500</v>
-      </c>
       <c r="I32" s="3">
+        <v>60000</v>
+      </c>
+      <c r="J32" s="3">
         <v>51900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>50800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>49600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>46500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-60500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-45500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-139200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-25300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-92000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-37800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-62800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-12100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-48800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-12600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>39900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E33" s="3">
         <v>19300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>83700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>108900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>35400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>267400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>43100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>71700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>43700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-31000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>11700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>8900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-9000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E35" s="3">
         <v>19300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>83700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>108900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>35400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>267400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>43100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>71700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>43700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-31000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>11700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>8900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-9000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,106 +2744,110 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E41" s="3">
         <v>8800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>11700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>132000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>109000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>75100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>51300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>24200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E42" s="3">
         <v>500</v>
       </c>
       <c r="F42" s="3">
+        <v>500</v>
+      </c>
+      <c r="G42" s="3">
         <v>100</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>4300</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>17800</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2794,87 +2884,93 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E43" s="3">
         <v>122500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>116600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>70300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>99100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>209900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>215700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>235300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>181500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>199000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>204000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>269600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>296200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>262600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>25800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>13700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>13200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>13700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>13600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3">
         <v>3600</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>8</v>
@@ -2882,372 +2978,387 @@
       <c r="H44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3">
         <v>3100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13000</v>
       </c>
-      <c r="P44" s="3" t="s">
+      <c r="Q44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>201400</v>
+      </c>
+      <c r="E45" s="3">
         <v>150600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>142300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>156800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>160900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>24300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>29200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5900</v>
-      </c>
-      <c r="R45" s="3">
-        <v>6000</v>
       </c>
       <c r="S45" s="3">
         <v>6000</v>
       </c>
       <c r="T45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="U45" s="3">
         <v>7800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>312600</v>
+      </c>
+      <c r="E46" s="3">
         <v>315000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>294800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>285900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>299300</v>
-      </c>
-      <c r="H46" s="3">
-        <v>257300</v>
       </c>
       <c r="I46" s="3">
         <v>257300</v>
       </c>
       <c r="J46" s="3">
+        <v>257300</v>
+      </c>
+      <c r="K46" s="3">
         <v>288500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>247800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>246200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>241900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>318800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>341800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>309500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>166600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>130300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>98200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>76200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>42800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>20400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>20900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>37500</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2105300</v>
+      </c>
+      <c r="E47" s="3">
         <v>2112300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2117900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2142000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2075900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2526300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2541000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2519200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2490100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2412900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2381300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2372600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2342300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2361300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1364800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1537900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1554400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1566700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1555200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1524400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1408500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1336800</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3811400</v>
+      </c>
+      <c r="E48" s="3">
         <v>3675900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3463700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3265000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3240200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2774500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2780800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2768500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2750500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2698300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2563800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2563300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2534100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2535100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>187000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>189400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>190800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>193400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>195800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>205300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>207300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>612800</v>
+      </c>
+      <c r="E49" s="3">
         <v>638900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>657600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>883200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>951700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>567900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>596700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>625900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>655000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>681600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>700500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>726900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>751800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>776900</v>
-      </c>
-      <c r="Q49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>8</v>
@@ -3261,8 +3372,8 @@
       <c r="U49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
@@ -3270,8 +3381,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,76 +3523,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>100</v>
+        <v>1900</v>
       </c>
       <c r="E52" s="3">
         <v>100</v>
       </c>
       <c r="F52" s="3">
+        <v>100</v>
+      </c>
+      <c r="G52" s="3">
         <v>1600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2400</v>
       </c>
-      <c r="K52" s="3" t="s">
+      <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>32300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>26400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>30900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3665,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7151000</v>
+      </c>
+      <c r="E54" s="3">
         <v>7030700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6814900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6860500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6860300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6447600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6496900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6286000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6226900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6124700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5919700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6007200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5996300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6013700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1724700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1865900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1853700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1842600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1799600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1756400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1642200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1588500</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,52 +3792,53 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>36600</v>
+      </c>
+      <c r="E57" s="3">
         <v>38700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>27200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>44500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>34000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>36200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>18300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16000</v>
-      </c>
-      <c r="O57" s="3">
-        <v>10900</v>
       </c>
       <c r="P57" s="3">
         <v>10900</v>
       </c>
       <c r="Q57" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
@@ -3719,52 +3850,55 @@
         <v>0</v>
       </c>
       <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
         <v>18800</v>
       </c>
-      <c r="V57" s="3" t="s">
+      <c r="W57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>200</v>
       </c>
-      <c r="X57" s="3" t="s">
+      <c r="Y57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>231800</v>
+      </c>
+      <c r="E58" s="3">
         <v>165100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>160100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>179400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>181800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>25000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>29200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>33400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>37800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>39800</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -3772,10 +3906,10 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>54300</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
@@ -3786,8 +3920,8 @@
       <c r="T58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3798,188 +3932,197 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>70700</v>
+      </c>
+      <c r="E59" s="3">
         <v>64400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>73500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>44500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>35300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>37300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>28700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>38800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>34200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>35500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>209900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>268700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>295100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>323400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>27200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>27500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>25100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>21900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>11200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>501800</v>
+      </c>
+      <c r="E60" s="3">
         <v>475300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>418600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>398700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>398900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>234000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>250100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>251100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>199400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>248300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>227800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>284700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>306000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>388600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>27200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>27500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>25100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>21900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>30000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>16500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3775000</v>
+      </c>
+      <c r="E61" s="3">
         <v>3588600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3375500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3292800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3273500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3520500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3577500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3622600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3647500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3536900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3368500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3447500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2971300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2894000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>657000</v>
       </c>
       <c r="R61" s="3">
         <v>657000</v>
@@ -3991,87 +4134,93 @@
         <v>657000</v>
       </c>
       <c r="U61" s="3">
+        <v>657000</v>
+      </c>
+      <c r="V61" s="3">
         <v>624000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>580000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>493000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>468000</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E62" s="3">
         <v>27600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>68600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>66800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>7000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>31400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>50700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>47700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>85800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>222700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>135300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>193700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>197500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>227500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>208600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>247800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>243500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>232300</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4429,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4340600</v>
+      </c>
+      <c r="E66" s="3">
         <v>4129800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3835900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3798000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3777600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3796400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3869900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3915500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3890100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3850000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6759500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6841700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7177700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7151500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2301900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2350100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2359900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2173600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2046100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1683600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1571900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1518000</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4811,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1781400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2616600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2976600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1720700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1206900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-973500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-723500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-929800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-902400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-863500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-958600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-941700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1181300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1137900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-577300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-484100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-506200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-369300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-391000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-400400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-402700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-402500</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5095,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1565700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2549700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-2976600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1720700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1206900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-973400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-530800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-838000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-905800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-636200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-839800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-834600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-1181300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-1137900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-577200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-484100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-506200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-331000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-246500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>72800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>70300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E81" s="3">
         <v>19300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>83700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>108900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>35400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>267400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>43100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>71700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>43700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-31000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>11700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>8900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-9000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,58 +5413,59 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E83" s="3">
         <v>42900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>42000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>39400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>38900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>38400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>37200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>36700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>30800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>67700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>65000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>66600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>61000</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>4100</v>
       </c>
       <c r="R83" s="3">
         <v>4100</v>
       </c>
       <c r="S83" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="T83" s="3">
         <v>4000</v>
@@ -5278,13 +5477,16 @@
         <v>4000</v>
       </c>
       <c r="W83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="X83" s="3">
         <v>8000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>129100</v>
+      </c>
+      <c r="E89" s="3">
         <v>176800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>144000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>214100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>125500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>153700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>178900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>174500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>111500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>119600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>159800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>184300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>170500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>98400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>51300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>57300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>57800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>43300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>26800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>50700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>86800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5937,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-127300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-74500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-107700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-58500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-39400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-58000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-67100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-85600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-101300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-58900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-47800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-93900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-47200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-32800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-26500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-131500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-260100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-111000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-109200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>105300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-62000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-103700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-134700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-201400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-246500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-69700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-147400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-49700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-19400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>7600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>12500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>1900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-13200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-37100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-126000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-175300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-97600</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,52 +6248,53 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>123700</v>
+      </c>
+      <c r="E96" s="3">
         <v>123200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>123000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>118200</v>
       </c>
-      <c r="G96" s="3">
-        <v>116000</v>
-      </c>
       <c r="H96" s="3">
+        <v>115200</v>
+      </c>
+      <c r="I96" s="3">
         <v>39500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>23500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>22000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>19600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>16900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
-        <v>-5600</v>
+        <v>0</v>
       </c>
       <c r="R96" s="3">
         <v>-5600</v>
@@ -6072,7 +6306,7 @@
         <v>-5600</v>
       </c>
       <c r="U96" s="3">
-        <v>0</v>
+        <v>-5600</v>
       </c>
       <c r="V96" s="3">
         <v>0</v>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,52 +6530,55 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E100" s="3">
         <v>88500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-49800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-97000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-228000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-86500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-70700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-42000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>90200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>122500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-95400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-30600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-133200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-80100</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-35900</v>
       </c>
       <c r="R100" s="3">
         <v>-35900</v>
@@ -6341,22 +6587,25 @@
         <v>-35900</v>
       </c>
       <c r="T100" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="U100" s="3">
         <v>-2900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>32400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>75400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>84400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6387,8 +6636,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6423,72 +6672,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E102" s="3">
         <v>5200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>23000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>33900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>23800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>27100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>22200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>KNTK</t>
   </si>
@@ -656,340 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>430400</v>
+      </c>
+      <c r="E8" s="3">
         <v>464000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>426700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>443300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>385700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>396400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>359500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>341400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>348900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>330300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>296200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>281000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>295500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>325200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>335600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>257200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>56300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>34500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>35600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>34100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>35300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>40200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>73000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>234600</v>
+      </c>
+      <c r="E9" s="3">
         <v>305800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>224700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>287000</v>
       </c>
-      <c r="G9" s="3">
-        <v>229900</v>
-      </c>
       <c r="H9" s="3">
+        <v>229700</v>
+      </c>
+      <c r="I9" s="3">
         <v>199000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>190600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>197100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>184300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>190700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>150400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>151900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>124400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>151100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>158600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>124400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>20600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>9600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>10700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>9400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>19100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>18900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>40200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>195800</v>
+      </c>
+      <c r="E10" s="3">
         <v>158100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>202000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>156300</v>
       </c>
-      <c r="G10" s="3">
-        <v>155800</v>
-      </c>
       <c r="H10" s="3">
+        <v>156000</v>
+      </c>
+      <c r="I10" s="3">
         <v>197400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>168900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>144300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>164500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>139600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>145800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>129200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>171100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>174100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>177000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>132800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>35700</v>
-      </c>
-      <c r="T10" s="3">
-        <v>24900</v>
       </c>
       <c r="U10" s="3">
         <v>24900</v>
       </c>
       <c r="V10" s="3">
+        <v>24900</v>
+      </c>
+      <c r="W10" s="3">
         <v>24700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>16200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>21300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>32800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1090,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,138 +1180,144 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-394100</v>
+      </c>
+      <c r="E14" s="3">
         <v>5800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>12400</v>
+      </c>
+      <c r="I14" s="3">
         <v>-28600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-59400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>12100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>22900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-4500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>160400</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1600</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>100800</v>
+      </c>
+      <c r="E15" s="3">
         <v>95400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>93800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>92700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>87900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>87600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>75100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>73600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>72700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>69900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>69500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>68900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>67700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>65000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>66600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>61000</v>
-      </c>
-      <c r="S15" s="3">
-        <v>4100</v>
       </c>
       <c r="T15" s="3">
         <v>4100</v>
       </c>
       <c r="U15" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="V15" s="3">
         <v>4000</v>
@@ -1307,13 +1329,16 @@
         <v>4000</v>
       </c>
       <c r="Y15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Z15" s="3">
         <v>8000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>360700</v>
+      </c>
+      <c r="E17" s="3">
         <v>438400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>349300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>424000</v>
       </c>
-      <c r="G17" s="3">
-        <v>355700</v>
-      </c>
       <c r="H17" s="3">
+        <v>349600</v>
+      </c>
+      <c r="I17" s="3">
         <v>322100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>302900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>311100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>286900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>289000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>246600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>253400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>250500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>279400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>317800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>233700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>192400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>20000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>22000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>23000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>21200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>42500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>69700</v>
+      </c>
+      <c r="E18" s="3">
         <v>25500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>77400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19200</v>
       </c>
-      <c r="G18" s="3">
-        <v>30000</v>
-      </c>
       <c r="H18" s="3">
+        <v>36100</v>
+      </c>
+      <c r="I18" s="3">
         <v>74300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>56500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>30300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>61900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>41300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>49600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>27600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>45000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>45800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>17800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>23500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-136100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>14500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>13000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>19000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>30500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,355 +1545,368 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-58300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-61100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-57500</v>
       </c>
-      <c r="G20" s="3">
-        <v>-43500</v>
-      </c>
       <c r="H20" s="3">
+        <v>-44300</v>
+      </c>
+      <c r="I20" s="3">
         <v>-53200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-56000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-60000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-51900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-50800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-49600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-46500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>60500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>45500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>139200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>25300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>92000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>37800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>62800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>12100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>48800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>12600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-39900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-44500</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>224800</v>
+      </c>
+      <c r="E21" s="3">
         <v>179200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>232300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>169400</v>
       </c>
-      <c r="G21" s="3">
-        <v>161500</v>
-      </c>
       <c r="H21" s="3">
+        <v>168400</v>
+      </c>
+      <c r="I21" s="3">
         <v>215100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>187500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>163900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>186500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>162000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>168700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>143000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>173200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>156300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>223500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>109900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-40000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>56400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>80500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>29100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>65000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>35600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-21900</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>59400</v>
+      </c>
+      <c r="E22" s="3">
         <v>61700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>56500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>55700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>49700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>66000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>54000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>47500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>75400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>45000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>16100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>69300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>56700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>40500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>25300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>26800</v>
-      </c>
-      <c r="S22" s="3">
-        <v>2700</v>
       </c>
       <c r="T22" s="3">
         <v>2700</v>
       </c>
       <c r="U22" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="V22" s="3">
         <v>2600</v>
       </c>
       <c r="W22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="X22" s="3">
         <v>1200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>456400</v>
+      </c>
+      <c r="E23" s="3">
         <v>16700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>81700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>91900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>118200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>39200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>32400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>44400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>72000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>48800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>50800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>131600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>22100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-46800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>49700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>73800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>22500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>59800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>31200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-234900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>300</v>
-      </c>
-      <c r="N24" s="3">
-        <v>400</v>
       </c>
       <c r="O24" s="3">
         <v>400</v>
       </c>
       <c r="P24" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q24" s="3">
         <v>1400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
@@ -1878,13 +1923,16 @@
         <v>0</v>
       </c>
       <c r="Y24" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>416700</v>
+      </c>
+      <c r="E26" s="3">
         <v>15500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>74400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>19300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>16200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>83700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>108900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>35400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>267400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>43100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>71700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>48500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>49400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>131400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>21400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-46800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>49700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>73800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>22500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>59800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>31200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-25400</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>139800</v>
+      </c>
+      <c r="E27" s="3">
         <v>1900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>20200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>32600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>243000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>43700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>3900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-31000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>5200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>11700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>8900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2253,8 +2313,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E32" s="3">
         <v>58300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>61100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>57500</v>
       </c>
-      <c r="G32" s="3">
-        <v>43500</v>
-      </c>
       <c r="H32" s="3">
+        <v>44300</v>
+      </c>
+      <c r="I32" s="3">
         <v>53200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>56000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>60000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>51900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>50800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>49600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>46500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-60500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-45500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-139200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-25300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-92000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-37800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-62800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-12100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-48800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>39900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>416700</v>
+      </c>
+      <c r="E33" s="3">
         <v>15500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>74400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>19300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>16200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>83700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>108900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>35400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>267400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>43100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>71700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>43700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>3900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-31000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>5200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>11700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>8900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>416700</v>
+      </c>
+      <c r="E35" s="3">
         <v>15500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>74400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>19300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>16200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>83700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>108900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>35400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>267400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>43100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>71700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>43700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>3900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-31000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>5200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>11700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>8900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,118 +2917,122 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E41" s="3">
         <v>7700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>11700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>17600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>132000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>109000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>75100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>51300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>24200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
         <v>400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>700</v>
-      </c>
-      <c r="F42" s="3">
-        <v>500</v>
       </c>
       <c r="G42" s="3">
         <v>500</v>
       </c>
       <c r="H42" s="3">
+        <v>500</v>
+      </c>
+      <c r="I42" s="3">
         <v>100</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>4300</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>17800</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -2980,87 +3069,93 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>85300</v>
+      </c>
+      <c r="E43" s="3">
         <v>77400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>62900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>122500</v>
       </c>
-      <c r="G43" s="3">
-        <v>116600</v>
-      </c>
       <c r="H43" s="3">
+        <v>111900</v>
+      </c>
+      <c r="I43" s="3">
         <v>70300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>99100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>209900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>215700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>235300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>181500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>199000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>204000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>269600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>296200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>262600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>25800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>12000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>13700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>13200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>12900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>13700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>13600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>8</v>
+      <c r="D44" s="3">
+        <v>4600</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>8</v>
@@ -3068,11 +3163,11 @@
       <c r="F44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3">
         <v>3600</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>8</v>
@@ -3080,402 +3175,417 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3">
         <v>3100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>13000</v>
       </c>
-      <c r="R44" s="3" t="s">
+      <c r="S44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>179400</v>
+      </c>
+      <c r="E45" s="3">
         <v>185700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>201400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>150600</v>
       </c>
-      <c r="G45" s="3">
-        <v>142300</v>
-      </c>
       <c r="H45" s="3">
+        <v>142000</v>
+      </c>
+      <c r="I45" s="3">
         <v>156800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>160900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>10300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>26600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>24300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>27200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>29200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5900</v>
-      </c>
-      <c r="T45" s="3">
-        <v>6000</v>
       </c>
       <c r="U45" s="3">
         <v>6000</v>
       </c>
       <c r="V45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="W45" s="3">
         <v>7800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>2100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>302000</v>
+      </c>
+      <c r="E46" s="3">
         <v>315100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>312600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>315000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>294800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>285900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>299300</v>
-      </c>
-      <c r="J46" s="3">
-        <v>257300</v>
       </c>
       <c r="K46" s="3">
         <v>257300</v>
       </c>
       <c r="L46" s="3">
+        <v>257300</v>
+      </c>
+      <c r="M46" s="3">
         <v>288500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>247800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>246200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>241900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>318800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>341800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>309500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>166600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>130300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>98200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>76200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>42800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>20400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>20900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>37500</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2008700</v>
+      </c>
+      <c r="E47" s="3">
         <v>2085500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2105300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2112300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2117900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2142000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2075900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2526300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2541000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2519200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2490100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2412900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2381300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2372600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2342300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2361300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1364800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1537900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1554400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1566700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1555200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1524400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1408500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1336800</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3937400</v>
+      </c>
+      <c r="E48" s="3">
         <v>3891400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3811400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3675900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3463700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3265000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3240200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2774500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2780800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2768500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2750500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2698300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2563800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2563300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2534100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2535100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>187000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>189400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>190800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>193400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>195800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>205300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>207300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>558300</v>
+      </c>
+      <c r="E49" s="3">
         <v>589700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>612800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>638900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>657600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>883200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>951700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>567900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>596700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>625900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>655000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>681600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>700500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>726900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>751800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>776900</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>8</v>
@@ -3489,8 +3599,8 @@
       <c r="W49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
@@ -3498,8 +3608,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,82 +3762,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E52" s="3">
         <v>1100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1900</v>
-      </c>
-      <c r="F52" s="3">
-        <v>100</v>
       </c>
       <c r="G52" s="3">
         <v>100</v>
       </c>
       <c r="H52" s="3">
+        <v>100</v>
+      </c>
+      <c r="I52" s="3">
         <v>1600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2400</v>
       </c>
-      <c r="M52" s="3" t="s">
+      <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>32300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>25500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>26400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>30900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7095600</v>
+      </c>
+      <c r="E54" s="3">
         <v>7202100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7151000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7030700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6814900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6860500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6860300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6447600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6496900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6286000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6226900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6124700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5919700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6007200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5996300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6013700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1724700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1865900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1853700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1842600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1799600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1756400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1642200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1588500</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,58 +4053,59 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>42100</v>
+      </c>
+      <c r="E57" s="3">
         <v>31600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>36600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>38700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>27200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>44500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>34000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>36200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>18300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16000</v>
-      </c>
-      <c r="Q57" s="3">
-        <v>10900</v>
       </c>
       <c r="R57" s="3">
         <v>10900</v>
       </c>
       <c r="S57" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
@@ -3987,58 +4117,61 @@
         <v>0</v>
       </c>
       <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
         <v>18800</v>
       </c>
-      <c r="X57" s="3" t="s">
+      <c r="Y57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>200</v>
       </c>
-      <c r="Z57" s="3" t="s">
+      <c r="AA57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>208900</v>
+      </c>
+      <c r="E58" s="3">
         <v>223200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>231800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>165100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>160100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>179400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>181800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>25000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>29200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>33400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>37800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>39800</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -4046,10 +4179,10 @@
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>54300</v>
-      </c>
-      <c r="S58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>8</v>
@@ -4060,8 +4193,8 @@
       <c r="V58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -4072,206 +4205,215 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E59" s="3">
         <v>62100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>70700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>64400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>73500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>44500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>35300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>37300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>28700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>38800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>34200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>35500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>209900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>268700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>295100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>323400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>27200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>27500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>25100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>21900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>440500</v>
+      </c>
+      <c r="E60" s="3">
         <v>504300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>501800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>475300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>418600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>398700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>398900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>234000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>250100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>251100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>199400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>248300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>227800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>284700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>306000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>388600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>27200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>27500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>25100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>21900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>30000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>16500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>12100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3656800</v>
+      </c>
+      <c r="E61" s="3">
         <v>3996200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3775000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3588600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3375500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3292800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3273500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3520500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3577500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3622600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3647500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3536900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3368500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3447500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2971300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2894000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>657000</v>
       </c>
       <c r="T61" s="3">
         <v>657000</v>
@@ -4283,93 +4425,99 @@
         <v>657000</v>
       </c>
       <c r="W61" s="3">
+        <v>657000</v>
+      </c>
+      <c r="X61" s="3">
         <v>624000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>580000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>493000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>468000</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E62" s="3">
         <v>25100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>27600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>68600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>66800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>31400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>50700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>47700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>85800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>222700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>135300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>193700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>197500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>227500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>208600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>247800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>243500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>232300</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4165200</v>
+      </c>
+      <c r="E66" s="3">
         <v>4576900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4340600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4129800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3835900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3798000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3777600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3796400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3869900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3915500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3890100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3850000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6759500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6841700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7177700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7151500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2301900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2350100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2359900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2173600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2046100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1683600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1571900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1518000</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4914,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-806100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1997700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1781400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-2616600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2976600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1720700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1206900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-973500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-723500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-929800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-902400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-863500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-958600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-941700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1181300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1137900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-577300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-484100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-506200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-369300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-391000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-400400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-402700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-402500</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-565400</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1775700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1565700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-2549700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-2976600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1720700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1206900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-973400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-530800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-838000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-905800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-636200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-839800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-834600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-1181300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-1137900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-577200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-484100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-506200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-331000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-246500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>72800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>70300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>416700</v>
+      </c>
+      <c r="E81" s="3">
         <v>15500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>74400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>19300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>16200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>83700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>108900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>35400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>267400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>43100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>71700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>43700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>3900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-31000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>5200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>11700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>8900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,8 +5810,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5622,55 +5820,55 @@
         <v>48700</v>
       </c>
       <c r="E83" s="3">
+        <v>48700</v>
+      </c>
+      <c r="F83" s="3">
         <v>43800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>42900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>42000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>39400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>38900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>38400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>37200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>34900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>36700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>67700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>65000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>66600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>61000</v>
-      </c>
-      <c r="S83" s="3">
-        <v>4100</v>
       </c>
       <c r="T83" s="3">
         <v>4100</v>
       </c>
       <c r="U83" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="V83" s="3">
         <v>4000</v>
@@ -5682,13 +5880,16 @@
         <v>4000</v>
       </c>
       <c r="Y83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="Z83" s="3">
         <v>8000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>110100</v>
+      </c>
+      <c r="E89" s="3">
         <v>188100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>129100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>176800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>144000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>214100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>125500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>153700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>178900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>174500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>111500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>119600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>159800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>184300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>170500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>98400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>51300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>57300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>57800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>43300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>26800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>50700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>86800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,82 +6378,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-134100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-156500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-127300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-74500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-107700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-58500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-39400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-58000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-67100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-85600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-101300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-58900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-47800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-93900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-47200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-32800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-26500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>363800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-171300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-131500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-260100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-111000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-109200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>105300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-62000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-103700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-134700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-201400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-246500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-69700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-147400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-49700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-19400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>7600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>12500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>1900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-13200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-37100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-126000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-175300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-97600</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,58 +6715,59 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>126300</v>
+      </c>
+      <c r="E96" s="3">
         <v>126900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>123700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>123200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>123000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>118200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>115200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>39500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>23500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>22000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>19600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>16900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-400</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
       <c r="S96" s="3">
-        <v>-5600</v>
+        <v>0</v>
       </c>
       <c r="T96" s="3">
         <v>-5600</v>
@@ -6546,7 +6779,7 @@
         <v>-5600</v>
       </c>
       <c r="W96" s="3">
-        <v>0</v>
+        <v>-5600</v>
       </c>
       <c r="X96" s="3">
         <v>0</v>
@@ -6557,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,58 +7021,61 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-477700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-19800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>88500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-49800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-97000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-228000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-86500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-70700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-42000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>90200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>122500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-95400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-133200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-80100</v>
-      </c>
-      <c r="S100" s="3">
-        <v>-35900</v>
       </c>
       <c r="T100" s="3">
         <v>-35900</v>
@@ -6839,22 +7084,25 @@
         <v>-35900</v>
       </c>
       <c r="V100" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="W100" s="3">
         <v>-2900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>32400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>75400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>84400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6891,8 +7139,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6927,78 +7175,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>4400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-12300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>23000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>33900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>23800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>27100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>22200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KNTK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>KNTK</t>
   </si>
@@ -656,352 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>410000</v>
+      </c>
+      <c r="E8" s="3">
         <v>430400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>464000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>426700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>443300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>385700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>396400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>359500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>341400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>348900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>330300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>296200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>281000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>295500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>325200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>335600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>257200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>56300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>34500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>35600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>34100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>35300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>40200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>73000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>259000</v>
+      </c>
+      <c r="E9" s="3">
         <v>234600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>305800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>224700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>287000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>229700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>199000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>190600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>197100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>184300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>190700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>150400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>151900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>124400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>151100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>158600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>124400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>20600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>9600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>10700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>9400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>19100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>18900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>40200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E10" s="3">
         <v>195800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>158100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>202000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>156300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>156000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>197400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>168900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>144300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>164500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>139600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>145800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>129200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>171100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>174100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>177000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>132800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>35700</v>
-      </c>
-      <c r="U10" s="3">
-        <v>24900</v>
       </c>
       <c r="V10" s="3">
         <v>24900</v>
       </c>
       <c r="W10" s="3">
+        <v>24900</v>
+      </c>
+      <c r="X10" s="3">
         <v>24700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>16200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>21300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>32800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>19900</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1106,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,144 +1200,150 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>-394100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>600</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>12400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-28600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-59400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>7700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>22900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-4500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>160400</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1600</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>101800</v>
+      </c>
+      <c r="E15" s="3">
         <v>100800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>95400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>93800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>92700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>87900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>87600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>75100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>73600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>72700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>69900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>69500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>68900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>67700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>65000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>66600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>61000</v>
-      </c>
-      <c r="T15" s="3">
-        <v>4100</v>
       </c>
       <c r="U15" s="3">
         <v>4100</v>
       </c>
       <c r="V15" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="W15" s="3">
         <v>4000</v>
@@ -1332,13 +1355,16 @@
         <v>4000</v>
       </c>
       <c r="Z15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AA15" s="3">
         <v>8000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>413800</v>
+      </c>
+      <c r="E17" s="3">
         <v>360700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>438400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>349300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>424000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>349600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>322100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>302900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>311100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>286900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>289000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>246600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>253400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>250500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>279400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>317800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>233700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>192400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>20000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>22000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>23000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>21200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>42500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22200</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E18" s="3">
         <v>69700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>25500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>77400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>19200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>36100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>74300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>56500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>30300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>61900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>41300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>49600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>27600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>45000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>45800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>17800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>23500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-136100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>14500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>13600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>12300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>19000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>30500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,370 +1579,383 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-51200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-54400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-58300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-61100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-57500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-44300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-53200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-56000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-60000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-51900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-50800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-49600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-46500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>60500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>45500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>139200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>25300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>92000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>37800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>62800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>12100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>48800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>12600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-39900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-44500</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>149200</v>
+      </c>
+      <c r="E21" s="3">
         <v>224800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>179200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>232300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>169400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>168400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>215100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>187500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>163900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>186500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>162000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>168700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>143000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>173200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>156300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>223500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>109900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-40000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>56400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>80500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>29100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>65000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>35600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-21900</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>53400</v>
+      </c>
+      <c r="E22" s="3">
         <v>59400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>61700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>56500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>55700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>49700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>66000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>54000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>47500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>75400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>45000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>69300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>56700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>40500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>25300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>26800</v>
-      </c>
-      <c r="T22" s="3">
-        <v>2700</v>
       </c>
       <c r="U22" s="3">
         <v>2700</v>
       </c>
       <c r="V22" s="3">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="W22" s="3">
         <v>2600</v>
       </c>
       <c r="X22" s="3">
+        <v>2600</v>
+      </c>
+      <c r="Y22" s="3">
         <v>1200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E23" s="3">
         <v>456400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>16700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>81700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>21800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>91900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>118200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>39200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>32400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>44400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>72000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>48800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>50800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>131600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>22100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-46800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>49700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>73800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>22500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>59800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>31200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-10000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-26100</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E24" s="3">
         <v>39700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-234900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>300</v>
-      </c>
-      <c r="O24" s="3">
-        <v>400</v>
       </c>
       <c r="P24" s="3">
         <v>400</v>
       </c>
       <c r="Q24" s="3">
+        <v>400</v>
+      </c>
+      <c r="R24" s="3">
         <v>1400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>700</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
@@ -1926,13 +1972,16 @@
         <v>0</v>
       </c>
       <c r="Z24" s="3">
-        <v>-700</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E26" s="3">
         <v>416700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>74400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>19300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>83700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>108900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>35400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>267400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>43100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>71700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>48500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>49400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>131400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>21400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-46800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>49700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>73800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>22500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>59800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>31200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-25400</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="E27" s="3">
         <v>139800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>20200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>32600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>243000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>20600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>11300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>43700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>3900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-31000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>5200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>11700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>8900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2316,8 +2377,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,162 +2537,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E32" s="3">
         <v>54400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>58300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>61100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>57500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>44300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>53200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>56000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>60000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>51900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>50800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>49600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>46500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-60500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-45500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-139200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-25300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-92000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-37800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-62800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-12100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-48800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-12600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>39900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>44500</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E33" s="3">
         <v>416700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>74400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>19300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>83700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>108900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>35400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>267400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>43100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>71700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>43700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>3900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-31000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>5200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>11700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>8900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E35" s="3">
         <v>416700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>74400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>19300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>83700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>108900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>35400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>267400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>43100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>71700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>43700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>3900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-31000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>5200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>11700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>8900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,124 +3004,128 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>700</v>
+      </c>
+      <c r="E41" s="3">
         <v>4000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>11700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>17600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>132000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>109000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>75100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>51300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>24200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1600</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>700</v>
-      </c>
-      <c r="G42" s="3">
-        <v>500</v>
       </c>
       <c r="H42" s="3">
         <v>500</v>
       </c>
       <c r="I42" s="3">
+        <v>500</v>
+      </c>
+      <c r="J42" s="3">
         <v>100</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>4300</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>17800</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -3072,93 +3162,99 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>92700</v>
+      </c>
+      <c r="E43" s="3">
         <v>85300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>77400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>62900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>122500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>111900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>70300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>99100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>209900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>215700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>235300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>181500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>199000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>204000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>269600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>296200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>262600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>25800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>12000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>13700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>13200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>12900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>13700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>13600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>4600</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>8</v>
@@ -3166,11 +3262,11 @@
       <c r="G44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3">
         <v>3600</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>8</v>
@@ -3178,417 +3274,432 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
+      <c r="L44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="3">
         <v>3100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>13100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>13000</v>
       </c>
-      <c r="S44" s="3" t="s">
+      <c r="T44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>3900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>193100</v>
+      </c>
+      <c r="E45" s="3">
         <v>179400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>185700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>201400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>150600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>142000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>156800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>160900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>21600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>9900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>13800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>26600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>24300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>27200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>29200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5900</v>
-      </c>
-      <c r="U45" s="3">
-        <v>6000</v>
       </c>
       <c r="V45" s="3">
         <v>6000</v>
       </c>
       <c r="W45" s="3">
+        <v>6000</v>
+      </c>
+      <c r="X45" s="3">
         <v>7800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>318800</v>
+      </c>
+      <c r="E46" s="3">
         <v>302000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>315100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>312600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>315000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>294800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>285900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>299300</v>
-      </c>
-      <c r="K46" s="3">
-        <v>257300</v>
       </c>
       <c r="L46" s="3">
         <v>257300</v>
       </c>
       <c r="M46" s="3">
+        <v>257300</v>
+      </c>
+      <c r="N46" s="3">
         <v>288500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>247800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>246200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>241900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>318800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>341800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>309500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>166600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>130300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>98200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>76200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>42800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>20400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>20900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>37500</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1993200</v>
+      </c>
+      <c r="E47" s="3">
         <v>2008700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2085500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2105300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2112300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2117900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2142000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2075900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2526300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2541000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2519200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2490100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2412900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2381300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2372600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>2342300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2361300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1364800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1537900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1554400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>1566700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1555200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1524400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1408500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1336800</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3948100</v>
+      </c>
+      <c r="E48" s="3">
         <v>3937400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3891400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3811400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3675900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3463700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3265000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3240200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2774500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2780800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2768500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2750500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2698300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2563800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2563300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2534100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2535100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>187000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>189400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>190800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>193400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>195800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>205300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>207300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>208500</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>528300</v>
+      </c>
+      <c r="E49" s="3">
         <v>558300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>589700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>612800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>638900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>657600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>883200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>951700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>567900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>596700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>625900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>655000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>681600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>700500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>726900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>751800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>776900</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>8</v>
@@ -3602,8 +3713,8 @@
       <c r="X49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
@@ -3611,8 +3722,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,85 +3882,91 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>800</v>
+      </c>
+      <c r="E52" s="3">
         <v>1500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1900</v>
-      </c>
-      <c r="G52" s="3">
-        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
       </c>
       <c r="I52" s="3">
+        <v>100</v>
+      </c>
+      <c r="J52" s="3">
         <v>1600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2400</v>
       </c>
-      <c r="N52" s="3" t="s">
+      <c r="O52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>32300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>25500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>26400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>30900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5700</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7110700</v>
+      </c>
+      <c r="E54" s="3">
         <v>7095600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7202100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7151000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7030700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6814900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6860500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6860300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6447600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6496900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6286000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6226900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6124700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5919700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6007200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5996300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6013700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1724700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1865900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1853700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1842600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1799600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1756400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1642200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>1588500</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,61 +4184,62 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28700</v>
+      </c>
+      <c r="E57" s="3">
         <v>42100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>31600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>36600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>38700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>27200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>44500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>34000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>36200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>18300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16000</v>
-      </c>
-      <c r="R57" s="3">
-        <v>10900</v>
       </c>
       <c r="S57" s="3">
         <v>10900</v>
       </c>
       <c r="T57" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -4120,61 +4251,64 @@
         <v>0</v>
       </c>
       <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
         <v>18800</v>
       </c>
-      <c r="Y57" s="3" t="s">
+      <c r="Z57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>200</v>
       </c>
-      <c r="AA57" s="3" t="s">
+      <c r="AB57" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>227100</v>
+      </c>
+      <c r="E58" s="3">
         <v>208900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>223200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>231800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>165100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>160100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>179400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>181800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>25000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>29200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>33400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>37800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>39800</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -4182,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>54300</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>8</v>
@@ -4196,8 +4330,8 @@
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y58" s="3">
         <v>0</v>
@@ -4208,215 +4342,224 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>83100</v>
+      </c>
+      <c r="E59" s="3">
         <v>37900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>62100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>70700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>64400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>73500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>44500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>35300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>37300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>28700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>38800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>34200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>35500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>209900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>268700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>295100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>323400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>27200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>27500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>25100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>21900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>11200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>16500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>11900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>537100</v>
+      </c>
+      <c r="E60" s="3">
         <v>440500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>504300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>501800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>475300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>418600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>398700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>398900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>234000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>250100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>251100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>199400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>248300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>227800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>284700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>306000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>388600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>27200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>27500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>25100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>21900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>30000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>16500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>12700</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3662300</v>
+      </c>
+      <c r="E61" s="3">
         <v>3656800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3996200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3775000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3588600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3375500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3292800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3273500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3520500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3577500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3622600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3647500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3536900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3368500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3447500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2971300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2894000</v>
-      </c>
-      <c r="T61" s="3">
-        <v>657000</v>
       </c>
       <c r="U61" s="3">
         <v>657000</v>
@@ -4428,96 +4571,102 @@
         <v>657000</v>
       </c>
       <c r="X61" s="3">
+        <v>657000</v>
+      </c>
+      <c r="Y61" s="3">
         <v>624000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>580000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>493000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>468000</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E62" s="3">
         <v>14700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>25100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>27600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>68600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>66800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>7000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>31400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>50700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>47700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>85800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>222700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>135300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>193700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>197500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>227500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>208600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>247800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>243500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>232300</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4268600</v>
+      </c>
+      <c r="E66" s="3">
         <v>4165200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4576900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4340600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4129800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3835900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3798000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3777600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3796400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3869900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3915500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3890100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3850000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6759500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6841700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7177700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7151500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2301900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2350100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2359900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2173600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2046100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1683600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1571900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1518000</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1669300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-806100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1997700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1781400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-2616600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-2976600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1720700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1206900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-973500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-723500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-929800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-902400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-863500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-958600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-941700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1181300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1137900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-577300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-484100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-506200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-369300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-391000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-400400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-402700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-402500</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1669200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-565400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1775700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1565700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-2549700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-2976600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-1720700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-1206900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-973400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-530800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-838000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-905800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-636200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-839800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-834600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-1181300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-1137900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-577200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-484100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-506200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-331000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-246500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>72800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>70300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>70500</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E81" s="3">
         <v>416700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>74400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>19300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>83700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>108900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>35400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>267400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>43100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>71700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>43700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>3900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-31000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>5200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>11700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>8900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-8100</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,67 +6009,68 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>48700</v>
+        <v>62100</v>
       </c>
       <c r="E83" s="3">
         <v>48700</v>
       </c>
       <c r="F83" s="3">
+        <v>48700</v>
+      </c>
+      <c r="G83" s="3">
         <v>43800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>42900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>42000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>39400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>38900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>38400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>37200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>34900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>36700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>30800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>67700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>65000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>66600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>61000</v>
-      </c>
-      <c r="T83" s="3">
-        <v>4100</v>
       </c>
       <c r="U83" s="3">
         <v>4100</v>
       </c>
       <c r="V83" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="W83" s="3">
         <v>4000</v>
@@ -5883,13 +6082,16 @@
         <v>4000</v>
       </c>
       <c r="Z83" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AA83" s="3">
         <v>8000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>180400</v>
+      </c>
+      <c r="E89" s="3">
         <v>110100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>188100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>129100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>176800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>144000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>214100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>125500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>153700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>178900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>174500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>111500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>119600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>159800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>184300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>170500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>98400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>51300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>57300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>57800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>43300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>26800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>50700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>86800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>51500</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,85 +6599,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-134100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-156500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-127300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-74500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-107700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-58500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-39400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-58000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-67100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-85600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-101300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-58900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-47800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-93900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-47200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-32800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-26500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-19100</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-89100</v>
+      </c>
+      <c r="E94" s="3">
         <v>363800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-171300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-131500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-260100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-111000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-109200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>105300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-62000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-103700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-134700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-201400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-246500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-69700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-147400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-49700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-19400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>7600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>12500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>1900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-13200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-37100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-126000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-175300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-97600</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,61 +6949,62 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>131300</v>
+      </c>
+      <c r="E96" s="3">
         <v>126300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>126900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>123700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>123200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>123000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>118200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>115200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>39500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>23500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>22000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>19600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>16900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-400</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
       <c r="T96" s="3">
-        <v>-5600</v>
+        <v>0</v>
       </c>
       <c r="U96" s="3">
         <v>-5600</v>
@@ -6782,7 +7016,7 @@
         <v>-5600</v>
       </c>
       <c r="X96" s="3">
-        <v>0</v>
+        <v>-5600</v>
       </c>
       <c r="Y96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,61 +7267,64 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-94500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-477700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-19800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>88500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-49800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-97000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-228000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-86500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-70700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-42000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>90200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>122500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-95400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-30600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-133200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-80100</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-35900</v>
       </c>
       <c r="U100" s="3">
         <v>-35900</v>
@@ -7087,22 +7333,25 @@
         <v>-35900</v>
       </c>
       <c r="W100" s="3">
+        <v>-35900</v>
+      </c>
+      <c r="X100" s="3">
         <v>-2900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>32400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>75400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>84400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>59400</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7142,8 +7391,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7178,81 +7427,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-16800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>23000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>33900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>23800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>27100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>22200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13300</v>
       </c>
     </row>
